--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -6467,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:M211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6478,6 +6478,11 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6521,6 +6526,31 @@
           <t>effect_value</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>max_charges</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>recharge_time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>no_cost</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>spawns(id:weight)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fixed_spawns</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -6549,6 +6579,11 @@
       <c r="H2" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -6577,6 +6612,11 @@
       <c r="H3" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -6605,6 +6645,11 @@
       <c r="H4" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -6633,6 +6678,11 @@
       <c r="H5" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -6661,6 +6711,11 @@
       <c r="H6" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -6689,6 +6744,11 @@
       <c r="H7" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -6717,6 +6777,11 @@
       <c r="H8" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -6745,6 +6810,11 @@
       <c r="H9" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -6773,6 +6843,11 @@
       <c r="H10" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -6801,6 +6876,11 @@
       <c r="H11" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -6829,6 +6909,11 @@
       <c r="H12" s="3" t="n">
         <v>750</v>
       </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -6857,6 +6942,11 @@
       <c r="H13" s="3" t="n">
         <v>750</v>
       </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -6885,6 +6975,11 @@
       <c r="H14" s="3" t="n">
         <v>1250</v>
       </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -6913,6 +7008,11 @@
       <c r="H15" s="3" t="n">
         <v>1250</v>
       </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -6941,6 +7041,11 @@
       <c r="H16" s="3" t="n">
         <v>2000</v>
       </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -6969,6 +7074,11 @@
       <c r="H17" s="3" t="n">
         <v>2000</v>
       </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -6997,6 +7107,11 @@
       <c r="H18" s="3" t="n">
         <v>2000</v>
       </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -7025,6 +7140,11 @@
       <c r="H19" s="3" t="n">
         <v>3250</v>
       </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -7053,6 +7173,11 @@
       <c r="H20" s="3" t="n">
         <v>5000</v>
       </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -7081,6 +7206,11 @@
       <c r="H21" s="3" t="n">
         <v>5000</v>
       </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -7109,6 +7239,11 @@
       <c r="H22" s="3" t="n">
         <v>8000</v>
       </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -7137,6 +7272,11 @@
       <c r="H23" s="3" t="n">
         <v>8000</v>
       </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -7165,6 +7305,11 @@
       <c r="H24" s="3" t="n">
         <v>12500</v>
       </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -7193,6 +7338,11 @@
       <c r="H25" s="3" t="n">
         <v>12500</v>
       </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -7221,6 +7371,11 @@
       <c r="H26" s="3" t="n">
         <v>12500</v>
       </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -7249,6 +7404,11 @@
       <c r="H27" s="3" t="n">
         <v>20000</v>
       </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -7277,6 +7437,11 @@
       <c r="H28" s="3" t="n">
         <v>32500</v>
       </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -7305,6 +7470,11 @@
       <c r="H29" s="3" t="n">
         <v>32500</v>
       </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -7333,6 +7503,11 @@
       <c r="H30" s="3" t="n">
         <v>50000</v>
       </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -7361,6 +7536,11 @@
       <c r="H31" s="3" t="n">
         <v>50000</v>
       </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -7389,6 +7569,11 @@
       <c r="H32" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -7417,6 +7602,11 @@
       <c r="H33" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -7445,6 +7635,11 @@
       <c r="H34" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -7473,6 +7668,11 @@
       <c r="H35" s="3" t="n">
         <v>750</v>
       </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -7501,6 +7701,11 @@
       <c r="H36" s="3" t="n">
         <v>1250</v>
       </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -7529,6 +7734,11 @@
       <c r="H37" s="3" t="n">
         <v>2000</v>
       </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -7557,6 +7767,11 @@
       <c r="H38" s="3" t="n">
         <v>3250</v>
       </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -7585,6 +7800,11 @@
       <c r="H39" s="3" t="n">
         <v>5000</v>
       </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -7613,6 +7833,11 @@
       <c r="H40" s="3" t="n">
         <v>8000</v>
       </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -7641,6 +7866,11 @@
       <c r="H41" s="3" t="n">
         <v>12500</v>
       </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -7669,6 +7899,11 @@
       <c r="H42" s="3" t="n">
         <v>20000</v>
       </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -7697,6 +7932,11 @@
       <c r="H43" s="3" t="n">
         <v>32500</v>
       </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -7725,6 +7965,11 @@
       <c r="H44" s="3" t="n">
         <v>50000</v>
       </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -7753,6 +7998,11 @@
       <c r="H45" s="3" t="n">
         <v>80000</v>
       </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -7781,6 +8031,11 @@
       <c r="H46" s="3" t="n">
         <v>125000</v>
       </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -7809,6 +8064,11 @@
       <c r="H47" s="3" t="n">
         <v>50000</v>
       </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -7837,6 +8097,11 @@
       <c r="H48" s="3" t="n">
         <v>125000</v>
       </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -7865,6 +8130,11 @@
       <c r="H49" s="3" t="n">
         <v>80000</v>
       </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -7893,6 +8163,11 @@
       <c r="H50" s="3" t="n">
         <v>20000</v>
       </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -7921,6 +8196,11 @@
       <c r="H51" s="3" t="n">
         <v>125000</v>
       </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -7949,6 +8229,11 @@
       <c r="H52" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -7977,6 +8262,11 @@
       <c r="H53" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -8005,6 +8295,11 @@
       <c r="H54" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -8033,6 +8328,11 @@
       <c r="H55" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -8061,6 +8361,11 @@
       <c r="H56" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -8089,6 +8394,11 @@
       <c r="H57" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -8117,6 +8427,11 @@
       <c r="H58" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -8145,6 +8460,11 @@
       <c r="H59" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -8173,6 +8493,11 @@
       <c r="H60" s="3" t="n">
         <v>800</v>
       </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -8201,6 +8526,11 @@
       <c r="H61" s="3" t="n">
         <v>800</v>
       </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -8229,6 +8559,11 @@
       <c r="H62" s="3" t="n">
         <v>1500</v>
       </c>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -8257,6 +8592,11 @@
       <c r="H63" s="3" t="n">
         <v>1500</v>
       </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -8285,6 +8625,11 @@
       <c r="H64" s="3" t="n">
         <v>2500</v>
       </c>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -8313,6 +8658,11 @@
       <c r="H65" s="3" t="n">
         <v>2500</v>
       </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -8341,6 +8691,11 @@
       <c r="H66" s="3" t="n">
         <v>4000</v>
       </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -8369,6 +8724,11 @@
       <c r="H67" s="3" t="n">
         <v>4000</v>
       </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -8397,6 +8757,11 @@
       <c r="H68" s="3" t="n">
         <v>4000</v>
       </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -8425,6 +8790,11 @@
       <c r="H69" s="3" t="n">
         <v>6500</v>
       </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -8453,6 +8823,11 @@
       <c r="H70" s="3" t="n">
         <v>10000</v>
       </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -8481,6 +8856,11 @@
       <c r="H71" s="3" t="n">
         <v>10000</v>
       </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -8509,6 +8889,11 @@
       <c r="H72" s="3" t="n">
         <v>16000</v>
       </c>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -8537,6 +8922,11 @@
       <c r="H73" s="3" t="n">
         <v>16000</v>
       </c>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -8565,6 +8955,11 @@
       <c r="H74" s="3" t="n">
         <v>25000</v>
       </c>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -8593,6 +8988,11 @@
       <c r="H75" s="3" t="n">
         <v>25000</v>
       </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -8621,6 +9021,11 @@
       <c r="H76" s="3" t="n">
         <v>25000</v>
       </c>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -8649,6 +9054,11 @@
       <c r="H77" s="3" t="n">
         <v>40000</v>
       </c>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -8677,6 +9087,11 @@
       <c r="H78" s="3" t="n">
         <v>65000</v>
       </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -8705,6 +9120,11 @@
       <c r="H79" s="3" t="n">
         <v>65000</v>
       </c>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -8733,6 +9153,11 @@
       <c r="H80" s="3" t="n">
         <v>100000</v>
       </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -8761,6 +9186,11 @@
       <c r="H81" s="3" t="n">
         <v>100000</v>
       </c>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -8789,6 +9219,11 @@
       <c r="H82" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -8817,6 +9252,11 @@
       <c r="H83" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -8845,6 +9285,11 @@
       <c r="H84" s="3" t="n">
         <v>1500</v>
       </c>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -8873,6 +9318,11 @@
       <c r="H85" s="3" t="n">
         <v>2500</v>
       </c>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -8901,6 +9351,11 @@
       <c r="H86" s="3" t="n">
         <v>4000</v>
       </c>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -8929,6 +9384,11 @@
       <c r="H87" s="3" t="n">
         <v>6500</v>
       </c>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -8957,6 +9417,11 @@
       <c r="H88" s="3" t="n">
         <v>10000</v>
       </c>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -8985,6 +9450,11 @@
       <c r="H89" s="3" t="n">
         <v>16000</v>
       </c>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -9013,6 +9483,11 @@
       <c r="H90" s="3" t="n">
         <v>25000</v>
       </c>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -9041,6 +9516,11 @@
       <c r="H91" s="3" t="n">
         <v>40000</v>
       </c>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -9069,6 +9549,11 @@
       <c r="H92" s="3" t="n">
         <v>65000</v>
       </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -9097,6 +9582,11 @@
       <c r="H93" s="3" t="n">
         <v>100000</v>
       </c>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -9125,6 +9615,11 @@
       <c r="H94" s="3" t="n">
         <v>160000</v>
       </c>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -9153,6 +9648,11 @@
       <c r="H95" s="3" t="n">
         <v>250000</v>
       </c>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -9181,6 +9681,11 @@
       <c r="H96" s="3" t="n">
         <v>40000</v>
       </c>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
+      <c r="M96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -9209,6 +9714,11 @@
       <c r="H97" s="3" t="n">
         <v>250000</v>
       </c>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -9237,6 +9747,11 @@
       <c r="H98" s="3" t="n">
         <v>25000</v>
       </c>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
+      <c r="M98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -9265,6 +9780,11 @@
       <c r="H99" s="3" t="n">
         <v>100000</v>
       </c>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -9293,6 +9813,11 @@
       <c r="H100" s="3" t="n">
         <v>160000</v>
       </c>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr"/>
+      <c r="M100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -9321,6 +9846,11 @@
       <c r="H101" s="3" t="n">
         <v>250000</v>
       </c>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -9345,6 +9875,11 @@
       </c>
       <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr"/>
+      <c r="M102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -9369,6 +9904,11 @@
       </c>
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -9393,6 +9933,11 @@
       </c>
       <c r="G104" s="3" t="inlineStr"/>
       <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr"/>
+      <c r="M104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9417,6 +9962,11 @@
       </c>
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9441,6 +9991,11 @@
       </c>
       <c r="G106" s="3" t="inlineStr"/>
       <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr"/>
+      <c r="M106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9465,6 +10020,11 @@
       </c>
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -9489,6 +10049,11 @@
       </c>
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr"/>
+      <c r="M108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9513,6 +10078,11 @@
       </c>
       <c r="G109" s="3" t="inlineStr"/>
       <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9537,6 +10107,11 @@
       </c>
       <c r="G110" s="3" t="inlineStr"/>
       <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr"/>
+      <c r="M110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -9561,6 +10136,11 @@
       </c>
       <c r="G111" s="3" t="inlineStr"/>
       <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9585,6 +10165,11 @@
       </c>
       <c r="G112" s="3" t="inlineStr"/>
       <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr"/>
+      <c r="M112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -9609,6 +10194,11 @@
       </c>
       <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -9633,6 +10223,11 @@
       </c>
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr"/>
+      <c r="M114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -9657,6 +10252,11 @@
       </c>
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr"/>
+      <c r="M115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -9681,6 +10281,11 @@
       </c>
       <c r="G116" s="3" t="inlineStr"/>
       <c r="H116" s="3" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -9705,6 +10310,11 @@
       </c>
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -9729,6 +10339,11 @@
       </c>
       <c r="G118" s="3" t="inlineStr"/>
       <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
+      <c r="M118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -9753,6 +10368,11 @@
       </c>
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -9777,6 +10397,11 @@
       </c>
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
+      <c r="M120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -9801,6 +10426,11 @@
       </c>
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -9825,6 +10455,11 @@
       </c>
       <c r="G122" s="3" t="inlineStr"/>
       <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
+      <c r="M122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -9849,6 +10484,11 @@
       </c>
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -9873,6 +10513,11 @@
       </c>
       <c r="G124" s="3" t="inlineStr"/>
       <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
+      <c r="M124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -9897,6 +10542,11 @@
       </c>
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -9921,6 +10571,11 @@
       </c>
       <c r="G126" s="3" t="inlineStr"/>
       <c r="H126" s="3" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
+      <c r="M126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -9945,6 +10600,11 @@
       </c>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -9969,6 +10629,11 @@
       </c>
       <c r="G128" s="3" t="inlineStr"/>
       <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
+      <c r="M128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -9993,6 +10658,11 @@
       </c>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -10017,6 +10687,11 @@
       </c>
       <c r="G130" s="3" t="inlineStr"/>
       <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr"/>
+      <c r="M130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -10041,6 +10716,11 @@
       </c>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -10065,6 +10745,11 @@
       </c>
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr"/>
+      <c r="M132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -10089,6 +10774,11 @@
       </c>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -10113,6 +10803,11 @@
       </c>
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
+      <c r="M134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -10137,6 +10832,11 @@
       </c>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
+      <c r="M135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -10161,6 +10861,11 @@
       </c>
       <c r="G136" s="3" t="inlineStr"/>
       <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr"/>
+      <c r="M136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -10185,6 +10890,11 @@
       </c>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
+      <c r="M137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -10209,6 +10919,11 @@
       </c>
       <c r="G138" s="3" t="inlineStr"/>
       <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="3" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr"/>
+      <c r="M138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -10233,6 +10948,11 @@
       </c>
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr"/>
+      <c r="M139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -10257,6 +10977,11 @@
       </c>
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr"/>
+      <c r="M140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -10281,6 +11006,11 @@
       </c>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr"/>
+      <c r="J141" s="3" t="inlineStr"/>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
+      <c r="M141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -10305,6 +11035,11 @@
       </c>
       <c r="G142" s="3" t="inlineStr"/>
       <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr"/>
+      <c r="M142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -10329,6 +11064,11 @@
       </c>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+      <c r="K143" s="3" t="inlineStr"/>
+      <c r="L143" s="3" t="inlineStr"/>
+      <c r="M143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -10353,6 +11093,11 @@
       </c>
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="3" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr"/>
+      <c r="M144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -10377,6 +11122,11 @@
       </c>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr"/>
+      <c r="M145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -10401,6 +11151,11 @@
       </c>
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr"/>
+      <c r="K146" s="3" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr"/>
+      <c r="M146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -10425,6 +11180,11 @@
       </c>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+      <c r="K147" s="3" t="inlineStr"/>
+      <c r="L147" s="3" t="inlineStr"/>
+      <c r="M147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -10449,6 +11209,11 @@
       </c>
       <c r="G148" s="3" t="inlineStr"/>
       <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr"/>
+      <c r="M148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -10473,6 +11238,11 @@
       </c>
       <c r="G149" s="3" t="inlineStr"/>
       <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr"/>
+      <c r="K149" s="3" t="inlineStr"/>
+      <c r="L149" s="3" t="inlineStr"/>
+      <c r="M149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -10497,6 +11267,11 @@
       </c>
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr"/>
+      <c r="M150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -10521,6 +11296,11 @@
       </c>
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr"/>
+      <c r="M151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -10547,8 +11327,21 @@
         <v>7</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K152" s="3" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>15101:100</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -10575,8 +11368,21 @@
         <v>7</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K153" s="3" t="inlineStr"/>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>15101:100</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -10603,8 +11409,21 @@
         <v>7</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K154" s="3" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>15101:100</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -10631,8 +11450,21 @@
         <v>7</v>
       </c>
       <c r="H155" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J155" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>15101:100</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -10659,8 +11491,21 @@
         <v>7</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K156" s="3" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>15102:100</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -10687,8 +11532,21 @@
         <v>7</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K157" s="3" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>15102:100</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -10715,8 +11573,21 @@
         <v>7</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K158" s="3" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>15102:100</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -10743,8 +11614,21 @@
         <v>7</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J159" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K159" s="3" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>15102:100</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -10771,8 +11655,21 @@
         <v>7</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K160" s="3" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>15104:100</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -10799,8 +11696,21 @@
         <v>7</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K161" s="3" t="inlineStr"/>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>15104:100</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -10827,8 +11737,21 @@
         <v>7</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J162" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K162" s="3" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>15104:100</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -10855,8 +11778,21 @@
         <v>7</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J163" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K163" s="3" t="inlineStr"/>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>15104:100</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -10883,8 +11819,21 @@
         <v>7</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K164" s="3" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>15108:100</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -10911,8 +11860,21 @@
         <v>7</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J165" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K165" s="3" t="inlineStr"/>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>15108:100</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -10939,8 +11901,21 @@
         <v>7</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J166" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K166" s="3" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>15108:100</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -10967,8 +11942,21 @@
         <v>7</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>15101</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J167" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>15108:100</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -10993,6 +11981,11 @@
       </c>
       <c r="G168" s="3" t="inlineStr"/>
       <c r="H168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="3" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr"/>
+      <c r="M168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -11017,6 +12010,11 @@
       </c>
       <c r="G169" s="3" t="inlineStr"/>
       <c r="H169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr"/>
+      <c r="J169" s="3" t="inlineStr"/>
+      <c r="K169" s="3" t="inlineStr"/>
+      <c r="L169" s="3" t="inlineStr"/>
+      <c r="M169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -11041,6 +12039,11 @@
       </c>
       <c r="G170" s="3" t="inlineStr"/>
       <c r="H170" s="3" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="3" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr"/>
+      <c r="M170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -11065,6 +12068,11 @@
       </c>
       <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="3" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
+      <c r="K171" s="3" t="inlineStr"/>
+      <c r="L171" s="3" t="inlineStr"/>
+      <c r="M171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -11089,6 +12097,11 @@
       </c>
       <c r="G172" s="3" t="inlineStr"/>
       <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="3" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr"/>
+      <c r="M172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -11113,6 +12126,11 @@
       </c>
       <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="inlineStr"/>
+      <c r="K173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr"/>
+      <c r="M173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -11137,6 +12155,11 @@
       </c>
       <c r="G174" s="3" t="inlineStr"/>
       <c r="H174" s="3" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="3" t="inlineStr"/>
+      <c r="L174" s="3" t="inlineStr"/>
+      <c r="M174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -11161,6 +12184,11 @@
       </c>
       <c r="G175" s="3" t="inlineStr"/>
       <c r="H175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr"/>
+      <c r="J175" s="3" t="inlineStr"/>
+      <c r="K175" s="3" t="inlineStr"/>
+      <c r="L175" s="3" t="inlineStr"/>
+      <c r="M175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -11185,6 +12213,11 @@
       </c>
       <c r="G176" s="3" t="inlineStr"/>
       <c r="H176" s="3" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="3" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr"/>
+      <c r="M176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -11209,6 +12242,11 @@
       </c>
       <c r="G177" s="3" t="inlineStr"/>
       <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr"/>
+      <c r="K177" s="3" t="inlineStr"/>
+      <c r="L177" s="3" t="inlineStr"/>
+      <c r="M177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -11233,6 +12271,11 @@
       </c>
       <c r="G178" s="3" t="inlineStr"/>
       <c r="H178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr"/>
+      <c r="M178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -11257,6 +12300,11 @@
       </c>
       <c r="G179" s="3" t="inlineStr"/>
       <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="inlineStr"/>
+      <c r="L179" s="3" t="inlineStr"/>
+      <c r="M179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -11281,6 +12329,11 @@
       </c>
       <c r="G180" s="3" t="inlineStr"/>
       <c r="H180" s="3" t="inlineStr"/>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="3" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr"/>
+      <c r="M180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -11305,6 +12358,11 @@
       </c>
       <c r="G181" s="3" t="inlineStr"/>
       <c r="H181" s="3" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+      <c r="K181" s="3" t="inlineStr"/>
+      <c r="L181" s="3" t="inlineStr"/>
+      <c r="M181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -11329,6 +12387,11 @@
       </c>
       <c r="G182" s="3" t="inlineStr"/>
       <c r="H182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="3" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr"/>
+      <c r="M182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -11353,6 +12416,11 @@
       </c>
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="3" t="inlineStr"/>
+      <c r="I183" s="3" t="inlineStr"/>
+      <c r="J183" s="3" t="inlineStr"/>
+      <c r="K183" s="3" t="inlineStr"/>
+      <c r="L183" s="3" t="inlineStr"/>
+      <c r="M183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -11377,6 +12445,11 @@
       </c>
       <c r="G184" s="3" t="inlineStr"/>
       <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="3" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr"/>
+      <c r="M184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -11401,6 +12474,11 @@
       </c>
       <c r="G185" s="3" t="inlineStr"/>
       <c r="H185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+      <c r="K185" s="3" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr"/>
+      <c r="M185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -11425,6 +12503,11 @@
       </c>
       <c r="G186" s="3" t="inlineStr"/>
       <c r="H186" s="3" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="3" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr"/>
+      <c r="M186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -11449,6 +12532,11 @@
       </c>
       <c r="G187" s="3" t="inlineStr"/>
       <c r="H187" s="3" t="inlineStr"/>
+      <c r="I187" s="3" t="inlineStr"/>
+      <c r="J187" s="3" t="inlineStr"/>
+      <c r="K187" s="3" t="inlineStr"/>
+      <c r="L187" s="3" t="inlineStr"/>
+      <c r="M187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -11473,6 +12561,11 @@
       </c>
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="3" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="3" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr"/>
+      <c r="M188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -11497,6 +12590,11 @@
       </c>
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="3" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr"/>
+      <c r="K189" s="3" t="inlineStr"/>
+      <c r="L189" s="3" t="inlineStr"/>
+      <c r="M189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -11521,6 +12619,11 @@
       </c>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="3" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr"/>
+      <c r="M190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -11545,6 +12648,11 @@
       </c>
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="3" t="inlineStr"/>
+      <c r="I191" s="3" t="inlineStr"/>
+      <c r="J191" s="3" t="inlineStr"/>
+      <c r="K191" s="3" t="inlineStr"/>
+      <c r="L191" s="3" t="inlineStr"/>
+      <c r="M191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -11569,6 +12677,11 @@
       </c>
       <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="3" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="3" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr"/>
+      <c r="M192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -11593,6 +12706,11 @@
       </c>
       <c r="G193" s="3" t="inlineStr"/>
       <c r="H193" s="3" t="inlineStr"/>
+      <c r="I193" s="3" t="inlineStr"/>
+      <c r="J193" s="3" t="inlineStr"/>
+      <c r="K193" s="3" t="inlineStr"/>
+      <c r="L193" s="3" t="inlineStr"/>
+      <c r="M193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -11617,6 +12735,11 @@
       </c>
       <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr"/>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="3" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr"/>
+      <c r="M194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -11641,6 +12764,11 @@
       </c>
       <c r="G195" s="3" t="inlineStr"/>
       <c r="H195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="inlineStr"/>
+      <c r="J195" s="3" t="inlineStr"/>
+      <c r="K195" s="3" t="inlineStr"/>
+      <c r="L195" s="3" t="inlineStr"/>
+      <c r="M195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -11665,6 +12793,11 @@
       </c>
       <c r="G196" s="3" t="inlineStr"/>
       <c r="H196" s="3" t="inlineStr"/>
+      <c r="I196" s="3" t="inlineStr"/>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr"/>
+      <c r="M196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -11689,6 +12822,11 @@
       </c>
       <c r="G197" s="3" t="inlineStr"/>
       <c r="H197" s="3" t="inlineStr"/>
+      <c r="I197" s="3" t="inlineStr"/>
+      <c r="J197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="inlineStr"/>
+      <c r="L197" s="3" t="inlineStr"/>
+      <c r="M197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -11713,6 +12851,11 @@
       </c>
       <c r="G198" s="3" t="inlineStr"/>
       <c r="H198" s="3" t="inlineStr"/>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr"/>
+      <c r="M198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -11737,6 +12880,11 @@
       </c>
       <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="3" t="inlineStr"/>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr"/>
+      <c r="K199" s="3" t="inlineStr"/>
+      <c r="L199" s="3" t="inlineStr"/>
+      <c r="M199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -11765,6 +12913,11 @@
       <c r="H200" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="I200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr"/>
+      <c r="M200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -11793,6 +12946,11 @@
       <c r="H201" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr"/>
+      <c r="M201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -11821,6 +12979,11 @@
       <c r="H202" s="3" t="n">
         <v>150</v>
       </c>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr"/>
+      <c r="M202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -11849,6 +13012,11 @@
       <c r="H203" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="I203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="inlineStr"/>
+      <c r="L203" s="3" t="inlineStr"/>
+      <c r="M203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -11877,6 +13045,11 @@
       <c r="H204" s="3" t="n">
         <v>250</v>
       </c>
+      <c r="I204" s="3" t="inlineStr"/>
+      <c r="J204" s="3" t="inlineStr"/>
+      <c r="K204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr"/>
+      <c r="M204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -11905,6 +13078,11 @@
       <c r="H205" s="3" t="n">
         <v>300</v>
       </c>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="inlineStr"/>
+      <c r="L205" s="3" t="inlineStr"/>
+      <c r="M205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -11933,6 +13111,11 @@
       <c r="H206" s="3" t="n">
         <v>350</v>
       </c>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+      <c r="K206" s="3" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr"/>
+      <c r="M206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -11961,6 +13144,11 @@
       <c r="H207" s="3" t="n">
         <v>400</v>
       </c>
+      <c r="I207" s="3" t="inlineStr"/>
+      <c r="J207" s="3" t="inlineStr"/>
+      <c r="K207" s="3" t="inlineStr"/>
+      <c r="L207" s="3" t="inlineStr"/>
+      <c r="M207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -11989,6 +13177,11 @@
       <c r="H208" s="3" t="n">
         <v>450</v>
       </c>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+      <c r="K208" s="3" t="inlineStr"/>
+      <c r="L208" s="3" t="inlineStr"/>
+      <c r="M208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -12017,6 +13210,11 @@
       <c r="H209" s="3" t="n">
         <v>500</v>
       </c>
+      <c r="I209" s="3" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+      <c r="K209" s="3" t="inlineStr"/>
+      <c r="L209" s="3" t="inlineStr"/>
+      <c r="M209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -12045,6 +13243,11 @@
       <c r="H210" s="3" t="n">
         <v>550</v>
       </c>
+      <c r="I210" s="3" t="inlineStr"/>
+      <c r="J210" s="3" t="inlineStr"/>
+      <c r="K210" s="3" t="inlineStr"/>
+      <c r="L210" s="3" t="inlineStr"/>
+      <c r="M210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -12073,6 +13276,11 @@
       <c r="H211" s="3" t="n">
         <v>600</v>
       </c>
+      <c r="I211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr"/>
+      <c r="K211" s="3" t="inlineStr"/>
+      <c r="L211" s="3" t="inlineStr"/>
+      <c r="M211" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12717,8 +13925,10 @@
       <c r="E2" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>1</v>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" s="3" t="n">
         <v>15</v>
@@ -12755,14 +13965,16 @@
       <c r="E3" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G3" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
@@ -12793,14 +14005,16 @@
       <c r="E4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -12831,14 +14045,16 @@
       <c r="E5" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G5" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -12869,14 +14085,16 @@
       <c r="E6" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G6" s="3" t="n">
         <v>35</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -12907,14 +14125,16 @@
       <c r="E7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -12945,14 +14165,16 @@
       <c r="E8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G8" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -12983,14 +14205,16 @@
       <c r="E9" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G9" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -13021,14 +14245,16 @@
       <c r="E10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G10" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -13059,14 +14285,16 @@
       <c r="E11" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G11" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -13097,14 +14325,16 @@
       <c r="E12" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G12" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -13135,14 +14365,16 @@
       <c r="E13" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1</v>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G13" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -13173,14 +14405,16 @@
       <c r="E14" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G14" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -13211,14 +14445,16 @@
       <c r="E15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G15" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -13249,14 +14485,16 @@
       <c r="E16" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>1</v>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G16" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -13287,14 +14525,16 @@
       <c r="E17" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G17" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -13325,14 +14565,16 @@
       <c r="E18" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -13363,14 +14605,16 @@
       <c r="E19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G19" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -13401,14 +14645,16 @@
       <c r="E20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>1</v>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -13439,14 +14685,16 @@
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1</v>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G21" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -13477,14 +14725,16 @@
       <c r="E22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>1</v>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G22" s="3" t="n">
         <v>35</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -13515,14 +14765,16 @@
       <c r="E23" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>1</v>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G23" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -13553,14 +14805,16 @@
       <c r="E24" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>1</v>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G24" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -13591,14 +14845,16 @@
       <c r="E25" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>1</v>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G25" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -13629,14 +14885,16 @@
       <c r="E26" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>1</v>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G26" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -13667,14 +14925,16 @@
       <c r="E27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G27" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -13705,14 +14965,16 @@
       <c r="E28" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G28" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -13743,14 +15005,16 @@
       <c r="E29" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G29" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -13781,14 +15045,16 @@
       <c r="E30" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G30" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -13819,14 +15085,16 @@
       <c r="E31" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>1</v>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G31" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
@@ -13857,14 +15125,16 @@
       <c r="E32" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G32" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -13895,14 +15165,16 @@
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G33" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
@@ -13933,8 +15205,10 @@
       <c r="E34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G34" s="3" t="n">
         <v>15</v>
@@ -13971,14 +15245,16 @@
       <c r="E35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>1</v>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G35" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
@@ -14009,14 +15285,16 @@
       <c r="E36" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1</v>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G36" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
@@ -14047,14 +15325,16 @@
       <c r="E37" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>1</v>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G37" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
@@ -14085,14 +15365,16 @@
       <c r="E38" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>1</v>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G38" s="3" t="n">
         <v>35</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
@@ -14123,14 +15405,16 @@
       <c r="E39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G39" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
@@ -14161,14 +15445,16 @@
       <c r="E40" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>1</v>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G40" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.92</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -14199,14 +15485,16 @@
       <c r="E41" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>1</v>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G41" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.74</v>
+        <v>1</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
@@ -14237,14 +15525,16 @@
       <c r="E42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G42" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
@@ -14275,14 +15565,16 @@
       <c r="E43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>1</v>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G43" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
@@ -14313,14 +15605,16 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>1</v>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G44" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
@@ -14351,14 +15645,16 @@
       <c r="E45" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>1</v>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G45" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
@@ -14389,14 +15685,16 @@
       <c r="E46" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>1</v>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G46" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
@@ -14427,14 +15725,16 @@
       <c r="E47" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>1</v>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G47" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
@@ -14465,14 +15765,16 @@
       <c r="E48" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>1</v>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G48" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
@@ -14503,14 +15805,16 @@
       <c r="E49" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>1</v>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G49" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
@@ -14541,14 +15845,16 @@
       <c r="E50" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G50" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
@@ -14579,14 +15885,16 @@
       <c r="E51" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G51" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
@@ -14617,14 +15925,16 @@
       <c r="E52" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G52" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
@@ -14655,14 +15965,16 @@
       <c r="E53" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G53" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
@@ -14693,14 +16005,16 @@
       <c r="E54" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G54" s="3" t="n">
         <v>35</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
@@ -14731,14 +16045,16 @@
       <c r="E55" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G55" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
@@ -14769,14 +16085,16 @@
       <c r="E56" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G56" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
@@ -14807,14 +16125,16 @@
       <c r="E57" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G57" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
@@ -14845,14 +16165,16 @@
       <c r="E58" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>1</v>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G58" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
@@ -14883,14 +16205,16 @@
       <c r="E59" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F59" s="3" t="n">
-        <v>1</v>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G59" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>1.61</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
@@ -14921,14 +16245,16 @@
       <c r="E60" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>1</v>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G60" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
@@ -14959,14 +16285,16 @@
       <c r="E61" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>1</v>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G61" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
@@ -14997,14 +16325,16 @@
       <c r="E62" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G62" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
@@ -15035,14 +16365,16 @@
       <c r="E63" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G63" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
@@ -15073,14 +16405,16 @@
       <c r="E64" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F64" s="3" t="n">
-        <v>1</v>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G64" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
@@ -15111,14 +16445,16 @@
       <c r="E65" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>1</v>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G65" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
@@ -15149,8 +16485,10 @@
       <c r="E66" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>1</v>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G66" s="3" t="n">
         <v>15</v>
@@ -15187,14 +16525,16 @@
       <c r="E67" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G67" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
@@ -15225,14 +16565,16 @@
       <c r="E68" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F68" s="3" t="n">
-        <v>1</v>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G68" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
@@ -15263,14 +16605,16 @@
       <c r="E69" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G69" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
@@ -15301,8 +16645,10 @@
       <c r="E70" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F70" s="3" t="n">
-        <v>1</v>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G70" s="3" t="n">
         <v>35</v>
@@ -15339,14 +16685,16 @@
       <c r="E71" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F71" s="3" t="n">
-        <v>1</v>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G71" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
@@ -15377,14 +16725,16 @@
       <c r="E72" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F72" s="3" t="n">
-        <v>1</v>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G72" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
@@ -15415,14 +16765,16 @@
       <c r="E73" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F73" s="3" t="n">
-        <v>1</v>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G73" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
@@ -15453,8 +16805,10 @@
       <c r="E74" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F74" s="3" t="n">
-        <v>1</v>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G74" s="3" t="n">
         <v>55</v>
@@ -15491,14 +16845,16 @@
       <c r="E75" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F75" s="3" t="n">
-        <v>1</v>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G75" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
@@ -15529,14 +16885,16 @@
       <c r="E76" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>1</v>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G76" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
@@ -15567,14 +16925,16 @@
       <c r="E77" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F77" s="3" t="n">
-        <v>1</v>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G77" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
@@ -15605,8 +16965,10 @@
       <c r="E78" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F78" s="3" t="n">
-        <v>1</v>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G78" s="3" t="n">
         <v>75</v>
@@ -15643,14 +17005,16 @@
       <c r="E79" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G79" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
@@ -15681,14 +17045,16 @@
       <c r="E80" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G80" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
@@ -15719,14 +17085,16 @@
       <c r="E81" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F81" s="3" t="n">
-        <v>1</v>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G81" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
@@ -15757,8 +17125,10 @@
       <c r="E82" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F82" s="3" t="n">
-        <v>1</v>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G82" s="3" t="n">
         <v>15</v>
@@ -15795,14 +17165,16 @@
       <c r="E83" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>1</v>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G83" s="3" t="n">
         <v>20</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>4.69</v>
+        <v>4</v>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
@@ -15833,14 +17205,16 @@
       <c r="E84" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>1</v>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G84" s="3" t="n">
         <v>25</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
@@ -15871,14 +17245,16 @@
       <c r="E85" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F85" s="3" t="n">
-        <v>1</v>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G85" s="3" t="n">
         <v>30</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
@@ -15909,14 +17285,16 @@
       <c r="E86" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F86" s="3" t="n">
-        <v>1</v>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G86" s="3" t="n">
         <v>35</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
@@ -15947,14 +17325,16 @@
       <c r="E87" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G87" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
@@ -15985,14 +17365,16 @@
       <c r="E88" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G88" s="3" t="n">
         <v>45</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
@@ -16023,14 +17405,16 @@
       <c r="E89" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G89" s="3" t="n">
         <v>50</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
@@ -16061,14 +17445,16 @@
       <c r="E90" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>1</v>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G90" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
@@ -16099,14 +17485,16 @@
       <c r="E91" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F91" s="3" t="n">
-        <v>1</v>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G91" s="3" t="n">
         <v>60</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
@@ -16137,14 +17525,16 @@
       <c r="E92" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F92" s="3" t="n">
-        <v>1</v>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G92" s="3" t="n">
         <v>65</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
@@ -16175,14 +17565,16 @@
       <c r="E93" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F93" s="3" t="n">
-        <v>1</v>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G93" s="3" t="n">
         <v>70</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
@@ -16213,14 +17605,16 @@
       <c r="E94" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F94" s="3" t="n">
-        <v>1</v>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G94" s="3" t="n">
         <v>75</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
@@ -16251,14 +17645,16 @@
       <c r="E95" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F95" s="3" t="n">
-        <v>1</v>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G95" s="3" t="n">
         <v>80</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
@@ -16289,14 +17685,16 @@
       <c r="E96" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F96" s="3" t="n">
-        <v>1</v>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G96" s="3" t="n">
         <v>85</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
@@ -16327,14 +17725,16 @@
       <c r="E97" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F97" s="3" t="n">
-        <v>1</v>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G97" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>

--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_regular" sheetId="1" r:id="R62af063bf3534aa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_recipe_product" sheetId="2" r:id="Rdd09839da90245ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_effect" sheetId="3" r:id="R624f3985225f4816"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_launcher" sheetId="4" r:id="Rde922a2f72b54389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_crafting" sheetId="5" r:id="R57b1bace1b2e4580"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_regular" sheetId="1" r:id="Rbc761c76f6e343f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_recipe_product" sheetId="2" r:id="R49f47e4498a04d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_effect" sheetId="3" r:id="R4ea6fe11db1a4b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_launcher" sheetId="4" r:id="R97f0e6f0d8934893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_crafting" sheetId="5" r:id="R173a7c84788b41e3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_regular" sheetId="1" r:id="Rf5f73bcdb3b54374"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_recipe_product" sheetId="2" r:id="Rdb513f15c65a4b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_effect" sheetId="3" r:id="R4a0354b5d34746eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_launcher" sheetId="4" r:id="R299f6fc6bb4243ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_crafting" sheetId="5" r:id="R48eaaadd519d4f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_regular" sheetId="1" r:id="Ra578eba0132b4c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_recipe_product" sheetId="2" r:id="R11e21cc007e4436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_effect" sheetId="3" r:id="Rb10aaac236504726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_launcher" sheetId="4" r:id="R81e88033c6084628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items_crafting" sheetId="5" r:id="Rd61ac12a4f404fb6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42,7 +42,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin"/>
@@ -50,11 +50,25 @@
       <x:top style="thin"/>
       <x:bottom style="thin"/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -65,6 +79,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -7134,6 +7149,2166 @@
         <x:v>1200000</x:v>
       </x:c>
     </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="B194" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>青灵枝</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>res://assets/items/icons_simple/1101.png</x:v>
+      </x:c>
+      <x:c r="E194" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F194" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G194" t="str">
+        <x:v>青灵枝是灵木一脉的1级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H194" t="str"/>
+      <x:c r="I194" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="n">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="B195" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>云纹木</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>res://assets/items/icons_simple/1102.png</x:v>
+      </x:c>
+      <x:c r="E195" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F195" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G195" t="str">
+        <x:v>云纹木是灵木一脉的2级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H195" t="str"/>
+      <x:c r="I195" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="B196" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>赤霞杉</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>res://assets/items/icons_simple/1103.png</x:v>
+      </x:c>
+      <x:c r="E196" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F196" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G196" t="str">
+        <x:v>赤霞杉是灵木一脉的3级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H196" t="str"/>
+      <x:c r="I196" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="n">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="B197" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>月桂灵木</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>res://assets/items/icons_simple/1104.png</x:v>
+      </x:c>
+      <x:c r="E197" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F197" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>月桂灵木是灵木一脉的4级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H197" t="str"/>
+      <x:c r="I197" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="n">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="B198" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>雷击桃木</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>res://assets/items/icons_simple/1105.png</x:v>
+      </x:c>
+      <x:c r="E198" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>雷击桃木是灵木一脉的5级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H198" t="str"/>
+      <x:c r="I198" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="B199" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>玄冰梧桐</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>res://assets/items/icons_simple/1106.png</x:v>
+      </x:c>
+      <x:c r="E199" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F199" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G199" t="str">
+        <x:v>玄冰梧桐是灵木一脉的6级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H199" t="str"/>
+      <x:c r="I199" t="n">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="n">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="B200" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>地脉沉香</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>res://assets/items/icons_simple/1107.png</x:v>
+      </x:c>
+      <x:c r="E200" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F200" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G200" t="str">
+        <x:v>地脉沉香是灵木一脉的7级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H200" t="str"/>
+      <x:c r="I200" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="n">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="B201" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>星辉紫檀</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>res://assets/items/icons_simple/1108.png</x:v>
+      </x:c>
+      <x:c r="E201" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F201" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G201" t="str">
+        <x:v>星辉紫檀是灵木一脉的8级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H201" t="str"/>
+      <x:c r="I201" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="n">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c r="B202" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>龙血古木</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
+        <x:v>res://assets/items/icons_simple/1109.png</x:v>
+      </x:c>
+      <x:c r="E202" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F202" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G202" t="str">
+        <x:v>龙血古木是灵木一脉的9级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H202" t="str"/>
+      <x:c r="I202" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="n">
+        <x:v>1110</x:v>
+      </x:c>
+      <x:c r="B203" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>凤栖神木</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
+        <x:v>res://assets/items/icons_simple/1110.png</x:v>
+      </x:c>
+      <x:c r="E203" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F203" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G203" t="str">
+        <x:v>凤栖神木是灵木一脉的10级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H203" t="str"/>
+      <x:c r="I203" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="B204" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>九幽冥木</x:v>
+      </x:c>
+      <x:c r="D204" t="str">
+        <x:v>res://assets/items/icons_simple/1111.png</x:v>
+      </x:c>
+      <x:c r="E204" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F204" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G204" t="str">
+        <x:v>九幽冥木是灵木一脉的11级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H204" t="str"/>
+      <x:c r="I204" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="n">
+        <x:v>1112</x:v>
+      </x:c>
+      <x:c r="B205" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>扶桑阳木</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
+        <x:v>res://assets/items/icons_simple/1112.png</x:v>
+      </x:c>
+      <x:c r="E205" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F205" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G205" t="str">
+        <x:v>扶桑阳木是灵木一脉的12级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H205" t="str"/>
+      <x:c r="I205" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="n">
+        <x:v>1113</x:v>
+      </x:c>
+      <x:c r="B206" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>建木灵芯</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>res://assets/items/icons_simple/1113.png</x:v>
+      </x:c>
+      <x:c r="E206" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F206" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G206" t="str">
+        <x:v>建木灵芯是灵木一脉的13级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H206" t="str"/>
+      <x:c r="I206" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="n">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="B207" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>菩提道木</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>res://assets/items/icons_simple/1114.png</x:v>
+      </x:c>
+      <x:c r="E207" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F207" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G207" t="str">
+        <x:v>菩提道木是灵木一脉的14级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H207" t="str"/>
+      <x:c r="I207" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="n">
+        <x:v>1115</x:v>
+      </x:c>
+      <x:c r="B208" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>鸿蒙祖木</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>res://assets/items/icons_simple/1115.png</x:v>
+      </x:c>
+      <x:c r="E208" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F208" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G208" t="str">
+        <x:v>鸿蒙祖木是灵木一脉的15级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H208" t="str"/>
+      <x:c r="I208" t="n">
+        <x:v>450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="n">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c r="B209" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>世界树心</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>res://assets/items/icons_simple/1116.png</x:v>
+      </x:c>
+      <x:c r="E209" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G209" t="str">
+        <x:v>世界树心是灵木一脉的16级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H209" t="str"/>
+      <x:c r="I209" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="n">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="B210" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>松露灵脂</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>res://assets/items/icons_simple/1201.png</x:v>
+      </x:c>
+      <x:c r="E210" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F210" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G210" t="str">
+        <x:v>松露灵脂是灵脂一脉的1级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H210" t="str"/>
+      <x:c r="I210" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="n">
+        <x:v>1202</x:v>
+      </x:c>
+      <x:c r="B211" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>青檀脂</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>res://assets/items/icons_simple/1202.png</x:v>
+      </x:c>
+      <x:c r="E211" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F211" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G211" t="str">
+        <x:v>青檀脂是灵脂一脉的2级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H211" t="str"/>
+      <x:c r="I211" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
+        <x:v>1203</x:v>
+      </x:c>
+      <x:c r="B212" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>赤枫脂</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>res://assets/items/icons_simple/1203.png</x:v>
+      </x:c>
+      <x:c r="E212" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F212" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G212" t="str">
+        <x:v>赤枫脂是灵脂一脉的3级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H212" t="str"/>
+      <x:c r="I212" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="B213" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>月桂凝脂</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
+        <x:v>res://assets/items/icons_simple/1204.png</x:v>
+      </x:c>
+      <x:c r="E213" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F213" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G213" t="str">
+        <x:v>月桂凝脂是灵脂一脉的4级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H213" t="str"/>
+      <x:c r="I213" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
+        <x:v>1205</x:v>
+      </x:c>
+      <x:c r="B214" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>桃木雷脂</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
+        <x:v>res://assets/items/icons_simple/1205.png</x:v>
+      </x:c>
+      <x:c r="E214" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F214" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G214" t="str">
+        <x:v>桃木雷脂是灵脂一脉的5级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H214" t="str"/>
+      <x:c r="I214" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="n">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="B215" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>冰梧寒脂</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>res://assets/items/icons_simple/1206.png</x:v>
+      </x:c>
+      <x:c r="E215" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F215" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G215" t="str">
+        <x:v>冰梧寒脂是灵脂一脉的6级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H215" t="str"/>
+      <x:c r="I215" t="n">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="n">
+        <x:v>1207</x:v>
+      </x:c>
+      <x:c r="B216" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>沉香地髓</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
+        <x:v>res://assets/items/icons_simple/1207.png</x:v>
+      </x:c>
+      <x:c r="E216" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F216" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G216" t="str">
+        <x:v>沉香地髓是灵脂一脉的7级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H216" t="str"/>
+      <x:c r="I216" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="n">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="B217" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>紫檀星脂</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
+        <x:v>res://assets/items/icons_simple/1208.png</x:v>
+      </x:c>
+      <x:c r="E217" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F217" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G217" t="str">
+        <x:v>紫檀星脂是灵脂一脉的8级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H217" t="str"/>
+      <x:c r="I217" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="n">
+        <x:v>1209</x:v>
+      </x:c>
+      <x:c r="B218" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>龙血木脂</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
+        <x:v>res://assets/items/icons_simple/1209.png</x:v>
+      </x:c>
+      <x:c r="E218" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F218" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G218" t="str">
+        <x:v>龙血木脂是灵脂一脉的9级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H218" t="str"/>
+      <x:c r="I218" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" t="n">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="B219" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>凤栖香脂</x:v>
+      </x:c>
+      <x:c r="D219" t="str">
+        <x:v>res://assets/items/icons_simple/1210.png</x:v>
+      </x:c>
+      <x:c r="E219" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F219" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G219" t="str">
+        <x:v>凤栖香脂是灵脂一脉的10级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H219" t="str"/>
+      <x:c r="I219" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="B220" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>九幽玄脂</x:v>
+      </x:c>
+      <x:c r="D220" t="str">
+        <x:v>res://assets/items/icons_simple/1211.png</x:v>
+      </x:c>
+      <x:c r="E220" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F220" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G220" t="str">
+        <x:v>九幽玄脂是灵脂一脉的11级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H220" t="str"/>
+      <x:c r="I220" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" t="n">
+        <x:v>1212</x:v>
+      </x:c>
+      <x:c r="B221" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>扶桑日脂</x:v>
+      </x:c>
+      <x:c r="D221" t="str">
+        <x:v>res://assets/items/icons_simple/1212.png</x:v>
+      </x:c>
+      <x:c r="E221" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F221" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G221" t="str">
+        <x:v>扶桑日脂是灵脂一脉的12级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H221" t="str"/>
+      <x:c r="I221" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="n">
+        <x:v>1213</x:v>
+      </x:c>
+      <x:c r="B222" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>建木玉脂</x:v>
+      </x:c>
+      <x:c r="D222" t="str">
+        <x:v>res://assets/items/icons_simple/1213.png</x:v>
+      </x:c>
+      <x:c r="E222" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F222" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G222" t="str">
+        <x:v>建木玉脂是灵脂一脉的13级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H222" t="str"/>
+      <x:c r="I222" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="n">
+        <x:v>1214</x:v>
+      </x:c>
+      <x:c r="B223" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>菩提心脂</x:v>
+      </x:c>
+      <x:c r="D223" t="str">
+        <x:v>res://assets/items/icons_simple/1214.png</x:v>
+      </x:c>
+      <x:c r="E223" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F223" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G223" t="str">
+        <x:v>菩提心脂是灵脂一脉的14级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H223" t="str"/>
+      <x:c r="I223" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="n">
+        <x:v>1215</x:v>
+      </x:c>
+      <x:c r="B224" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>鸿蒙源脂</x:v>
+      </x:c>
+      <x:c r="D224" t="str">
+        <x:v>res://assets/items/icons_simple/1215.png</x:v>
+      </x:c>
+      <x:c r="E224" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F224" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G224" t="str">
+        <x:v>鸿蒙源脂是灵脂一脉的15级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H224" t="str"/>
+      <x:c r="I224" t="n">
+        <x:v>450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="n">
+        <x:v>1216</x:v>
+      </x:c>
+      <x:c r="B225" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>太初神脂</x:v>
+      </x:c>
+      <x:c r="D225" t="str">
+        <x:v>res://assets/items/icons_simple/1216.png</x:v>
+      </x:c>
+      <x:c r="E225" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F225" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G225" t="str">
+        <x:v>太初神脂是灵脂一脉的16级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H225" t="str"/>
+      <x:c r="I225" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="n">
+        <x:v>1301</x:v>
+      </x:c>
+      <x:c r="B226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>青鳞灵鱼</x:v>
+      </x:c>
+      <x:c r="D226" t="str">
+        <x:v>res://assets/items/icons_simple/1301.png</x:v>
+      </x:c>
+      <x:c r="E226" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F226" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G226" t="str">
+        <x:v>青鳞灵鱼是灵鱼一脉的1级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H226" t="str"/>
+      <x:c r="I226" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="n">
+        <x:v>1302</x:v>
+      </x:c>
+      <x:c r="B227" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>银须鲫</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
+        <x:v>res://assets/items/icons_simple/1302.png</x:v>
+      </x:c>
+      <x:c r="E227" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F227" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G227" t="str">
+        <x:v>银须鲫是灵鱼一脉的2级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H227" t="str"/>
+      <x:c r="I227" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="n">
+        <x:v>1303</x:v>
+      </x:c>
+      <x:c r="B228" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>赤尾鲤</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
+        <x:v>res://assets/items/icons_simple/1303.png</x:v>
+      </x:c>
+      <x:c r="E228" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F228" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G228" t="str">
+        <x:v>赤尾鲤是灵鱼一脉的3级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H228" t="str"/>
+      <x:c r="I228" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="n">
+        <x:v>1304</x:v>
+      </x:c>
+      <x:c r="B229" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>月纹鳜</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
+        <x:v>res://assets/items/icons_simple/1304.png</x:v>
+      </x:c>
+      <x:c r="E229" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F229" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G229" t="str">
+        <x:v>月纹鳜是灵鱼一脉的4级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H229" t="str"/>
+      <x:c r="I229" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" t="n">
+        <x:v>1305</x:v>
+      </x:c>
+      <x:c r="B230" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>雷鳍鲶</x:v>
+      </x:c>
+      <x:c r="D230" t="str">
+        <x:v>res://assets/items/icons_simple/1305.png</x:v>
+      </x:c>
+      <x:c r="E230" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F230" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G230" t="str">
+        <x:v>雷鳍鲶是灵鱼一脉的5级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H230" t="str"/>
+      <x:c r="I230" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="B231" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>冰魄鲑</x:v>
+      </x:c>
+      <x:c r="D231" t="str">
+        <x:v>res://assets/items/icons_simple/1306.png</x:v>
+      </x:c>
+      <x:c r="E231" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F231" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G231" t="str">
+        <x:v>冰魄鲑是灵鱼一脉的6级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H231" t="str"/>
+      <x:c r="I231" t="n">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" t="n">
+        <x:v>1307</x:v>
+      </x:c>
+      <x:c r="B232" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>地脉鳅</x:v>
+      </x:c>
+      <x:c r="D232" t="str">
+        <x:v>res://assets/items/icons_simple/1307.png</x:v>
+      </x:c>
+      <x:c r="E232" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F232" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G232" t="str">
+        <x:v>地脉鳅是灵鱼一脉的7级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H232" t="str"/>
+      <x:c r="I232" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" t="n">
+        <x:v>1308</x:v>
+      </x:c>
+      <x:c r="B233" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>星斑鲷</x:v>
+      </x:c>
+      <x:c r="D233" t="str">
+        <x:v>res://assets/items/icons_simple/1308.png</x:v>
+      </x:c>
+      <x:c r="E233" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F233" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G233" t="str">
+        <x:v>星斑鲷是灵鱼一脉的8级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H233" t="str"/>
+      <x:c r="I233" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" t="n">
+        <x:v>1309</x:v>
+      </x:c>
+      <x:c r="B234" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>龙须鲤</x:v>
+      </x:c>
+      <x:c r="D234" t="str">
+        <x:v>res://assets/items/icons_simple/1309.png</x:v>
+      </x:c>
+      <x:c r="E234" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F234" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G234" t="str">
+        <x:v>龙须鲤是灵鱼一脉的9级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H234" t="str"/>
+      <x:c r="I234" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" t="n">
+        <x:v>1310</x:v>
+      </x:c>
+      <x:c r="B235" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>凤尾锦鲤</x:v>
+      </x:c>
+      <x:c r="D235" t="str">
+        <x:v>res://assets/items/icons_simple/1310.png</x:v>
+      </x:c>
+      <x:c r="E235" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F235" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G235" t="str">
+        <x:v>凤尾锦鲤是灵鱼一脉的10级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H235" t="str"/>
+      <x:c r="I235" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" t="n">
+        <x:v>1311</x:v>
+      </x:c>
+      <x:c r="B236" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>九幽玄鱼</x:v>
+      </x:c>
+      <x:c r="D236" t="str">
+        <x:v>res://assets/items/icons_simple/1311.png</x:v>
+      </x:c>
+      <x:c r="E236" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F236" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G236" t="str">
+        <x:v>九幽玄鱼是灵鱼一脉的11级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H236" t="str"/>
+      <x:c r="I236" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" t="n">
+        <x:v>1312</x:v>
+      </x:c>
+      <x:c r="B237" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>扶桑金鲤</x:v>
+      </x:c>
+      <x:c r="D237" t="str">
+        <x:v>res://assets/items/icons_simple/1312.png</x:v>
+      </x:c>
+      <x:c r="E237" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F237" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G237" t="str">
+        <x:v>扶桑金鲤是灵鱼一脉的12级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H237" t="str"/>
+      <x:c r="I237" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" t="n">
+        <x:v>1313</x:v>
+      </x:c>
+      <x:c r="B238" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>建木游龙</x:v>
+      </x:c>
+      <x:c r="D238" t="str">
+        <x:v>res://assets/items/icons_simple/1313.png</x:v>
+      </x:c>
+      <x:c r="E238" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F238" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G238" t="str">
+        <x:v>建木游龙是灵鱼一脉的13级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H238" t="str"/>
+      <x:c r="I238" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="B239" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>菩提慧鱼</x:v>
+      </x:c>
+      <x:c r="D239" t="str">
+        <x:v>res://assets/items/icons_simple/1314.png</x:v>
+      </x:c>
+      <x:c r="E239" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F239" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G239" t="str">
+        <x:v>菩提慧鱼是灵鱼一脉的14级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H239" t="str"/>
+      <x:c r="I239" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" t="n">
+        <x:v>1315</x:v>
+      </x:c>
+      <x:c r="B240" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>鸿蒙鲲苗</x:v>
+      </x:c>
+      <x:c r="D240" t="str">
+        <x:v>res://assets/items/icons_simple/1315.png</x:v>
+      </x:c>
+      <x:c r="E240" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F240" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G240" t="str">
+        <x:v>鸿蒙鲲苗是灵鱼一脉的15级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H240" t="str"/>
+      <x:c r="I240" t="n">
+        <x:v>450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" t="n">
+        <x:v>1316</x:v>
+      </x:c>
+      <x:c r="B241" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>太初神鲲</x:v>
+      </x:c>
+      <x:c r="D241" t="str">
+        <x:v>res://assets/items/icons_simple/1316.png</x:v>
+      </x:c>
+      <x:c r="E241" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F241" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G241" t="str">
+        <x:v>太初神鲲是灵鱼一脉的16级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H241" t="str"/>
+      <x:c r="I241" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" t="n">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="B242" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>清水灵珠</x:v>
+      </x:c>
+      <x:c r="D242" t="str">
+        <x:v>res://assets/items/icons_simple/1401.png</x:v>
+      </x:c>
+      <x:c r="E242" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F242" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G242" t="str">
+        <x:v>清水灵珠是灵珠一脉的1级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H242" t="str"/>
+      <x:c r="I242" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" t="n">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="B243" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>青波珠</x:v>
+      </x:c>
+      <x:c r="D243" t="str">
+        <x:v>res://assets/items/icons_simple/1402.png</x:v>
+      </x:c>
+      <x:c r="E243" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F243" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G243" t="str">
+        <x:v>青波珠是灵珠一脉的2级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H243" t="str"/>
+      <x:c r="I243" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="n">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="B244" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>赤潮珠</x:v>
+      </x:c>
+      <x:c r="D244" t="str">
+        <x:v>res://assets/items/icons_simple/1403.png</x:v>
+      </x:c>
+      <x:c r="E244" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F244" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G244" t="str">
+        <x:v>赤潮珠是灵珠一脉的3级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H244" t="str"/>
+      <x:c r="I244" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="n">
+        <x:v>1404</x:v>
+      </x:c>
+      <x:c r="B245" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" t="str">
+        <x:v>月华珠</x:v>
+      </x:c>
+      <x:c r="D245" t="str">
+        <x:v>res://assets/items/icons_simple/1404.png</x:v>
+      </x:c>
+      <x:c r="E245" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F245" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G245" t="str">
+        <x:v>月华珠是灵珠一脉的4级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H245" t="str"/>
+      <x:c r="I245" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="n">
+        <x:v>1405</x:v>
+      </x:c>
+      <x:c r="B246" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C246" t="str">
+        <x:v>雷鸣珠</x:v>
+      </x:c>
+      <x:c r="D246" t="str">
+        <x:v>res://assets/items/icons_simple/1405.png</x:v>
+      </x:c>
+      <x:c r="E246" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F246" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G246" t="str">
+        <x:v>雷鸣珠是灵珠一脉的5级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H246" t="str"/>
+      <x:c r="I246" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" t="n">
+        <x:v>1406</x:v>
+      </x:c>
+      <x:c r="B247" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C247" t="str">
+        <x:v>玄冰珠</x:v>
+      </x:c>
+      <x:c r="D247" t="str">
+        <x:v>res://assets/items/icons_simple/1406.png</x:v>
+      </x:c>
+      <x:c r="E247" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F247" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G247" t="str">
+        <x:v>玄冰珠是灵珠一脉的6级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H247" t="str"/>
+      <x:c r="I247" t="n">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" t="n">
+        <x:v>1407</x:v>
+      </x:c>
+      <x:c r="B248" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C248" t="str">
+        <x:v>地泉珠</x:v>
+      </x:c>
+      <x:c r="D248" t="str">
+        <x:v>res://assets/items/icons_simple/1407.png</x:v>
+      </x:c>
+      <x:c r="E248" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F248" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G248" t="str">
+        <x:v>地泉珠是灵珠一脉的7级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H248" t="str"/>
+      <x:c r="I248" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" t="n">
+        <x:v>1408</x:v>
+      </x:c>
+      <x:c r="B249" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C249" t="str">
+        <x:v>星澜珠</x:v>
+      </x:c>
+      <x:c r="D249" t="str">
+        <x:v>res://assets/items/icons_simple/1408.png</x:v>
+      </x:c>
+      <x:c r="E249" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F249" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G249" t="str">
+        <x:v>星澜珠是灵珠一脉的8级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H249" t="str"/>
+      <x:c r="I249" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" t="n">
+        <x:v>1409</x:v>
+      </x:c>
+      <x:c r="B250" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C250" t="str">
+        <x:v>龙涎珠</x:v>
+      </x:c>
+      <x:c r="D250" t="str">
+        <x:v>res://assets/items/icons_simple/1409.png</x:v>
+      </x:c>
+      <x:c r="E250" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F250" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G250" t="str">
+        <x:v>龙涎珠是灵珠一脉的9级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H250" t="str"/>
+      <x:c r="I250" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" t="n">
+        <x:v>1410</x:v>
+      </x:c>
+      <x:c r="B251" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C251" t="str">
+        <x:v>凤泪珠</x:v>
+      </x:c>
+      <x:c r="D251" t="str">
+        <x:v>res://assets/items/icons_simple/1410.png</x:v>
+      </x:c>
+      <x:c r="E251" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F251" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G251" t="str">
+        <x:v>凤泪珠是灵珠一脉的10级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H251" t="str"/>
+      <x:c r="I251" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" t="n">
+        <x:v>1411</x:v>
+      </x:c>
+      <x:c r="B252" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C252" t="str">
+        <x:v>九幽玄珠</x:v>
+      </x:c>
+      <x:c r="D252" t="str">
+        <x:v>res://assets/items/icons_simple/1411.png</x:v>
+      </x:c>
+      <x:c r="E252" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F252" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G252" t="str">
+        <x:v>九幽玄珠是灵珠一脉的11级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H252" t="str"/>
+      <x:c r="I252" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="n">
+        <x:v>1412</x:v>
+      </x:c>
+      <x:c r="B253" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C253" t="str">
+        <x:v>扶桑日珠</x:v>
+      </x:c>
+      <x:c r="D253" t="str">
+        <x:v>res://assets/items/icons_simple/1412.png</x:v>
+      </x:c>
+      <x:c r="E253" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F253" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G253" t="str">
+        <x:v>扶桑日珠是灵珠一脉的12级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H253" t="str"/>
+      <x:c r="I253" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" t="n">
+        <x:v>1413</x:v>
+      </x:c>
+      <x:c r="B254" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C254" t="str">
+        <x:v>建木碧珠</x:v>
+      </x:c>
+      <x:c r="D254" t="str">
+        <x:v>res://assets/items/icons_simple/1413.png</x:v>
+      </x:c>
+      <x:c r="E254" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F254" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G254" t="str">
+        <x:v>建木碧珠是灵珠一脉的13级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H254" t="str"/>
+      <x:c r="I254" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" t="n">
+        <x:v>1414</x:v>
+      </x:c>
+      <x:c r="B255" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C255" t="str">
+        <x:v>菩提心珠</x:v>
+      </x:c>
+      <x:c r="D255" t="str">
+        <x:v>res://assets/items/icons_simple/1414.png</x:v>
+      </x:c>
+      <x:c r="E255" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F255" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G255" t="str">
+        <x:v>菩提心珠是灵珠一脉的14级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H255" t="str"/>
+      <x:c r="I255" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" t="n">
+        <x:v>1415</x:v>
+      </x:c>
+      <x:c r="B256" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C256" t="str">
+        <x:v>鸿蒙源珠</x:v>
+      </x:c>
+      <x:c r="D256" t="str">
+        <x:v>res://assets/items/icons_simple/1415.png</x:v>
+      </x:c>
+      <x:c r="E256" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F256" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G256" t="str">
+        <x:v>鸿蒙源珠是灵珠一脉的15级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H256" t="str"/>
+      <x:c r="I256" t="n">
+        <x:v>450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" t="n">
+        <x:v>1416</x:v>
+      </x:c>
+      <x:c r="B257" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C257" t="str">
+        <x:v>太初神珠</x:v>
+      </x:c>
+      <x:c r="D257" t="str">
+        <x:v>res://assets/items/icons_simple/1416.png</x:v>
+      </x:c>
+      <x:c r="E257" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F257" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G257" t="str">
+        <x:v>太初神珠是灵珠一脉的16级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H257" t="str"/>
+      <x:c r="I257" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" t="n">
+        <x:v>1501</x:v>
+      </x:c>
+      <x:c r="B258" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C258" t="str">
+        <x:v>青白玉</x:v>
+      </x:c>
+      <x:c r="D258" t="str">
+        <x:v>res://assets/items/icons_simple/1501.png</x:v>
+      </x:c>
+      <x:c r="E258" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F258" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G258" t="str">
+        <x:v>青白玉是玉石一脉的1级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H258" t="str"/>
+      <x:c r="I258" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" t="n">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="B259" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C259" t="str">
+        <x:v>云纹玉</x:v>
+      </x:c>
+      <x:c r="D259" t="str">
+        <x:v>res://assets/items/icons_simple/1502.png</x:v>
+      </x:c>
+      <x:c r="E259" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F259" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G259" t="str">
+        <x:v>云纹玉是玉石一脉的2级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H259" t="str"/>
+      <x:c r="I259" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" t="n">
+        <x:v>1503</x:v>
+      </x:c>
+      <x:c r="B260" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C260" t="str">
+        <x:v>赤霞玉</x:v>
+      </x:c>
+      <x:c r="D260" t="str">
+        <x:v>res://assets/items/icons_simple/1503.png</x:v>
+      </x:c>
+      <x:c r="E260" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F260" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G260" t="str">
+        <x:v>赤霞玉是玉石一脉的3级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H260" t="str"/>
+      <x:c r="I260" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" t="n">
+        <x:v>1504</x:v>
+      </x:c>
+      <x:c r="B261" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" t="str">
+        <x:v>月华玉</x:v>
+      </x:c>
+      <x:c r="D261" t="str">
+        <x:v>res://assets/items/icons_simple/1504.png</x:v>
+      </x:c>
+      <x:c r="E261" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F261" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G261" t="str">
+        <x:v>月华玉是玉石一脉的4级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H261" t="str"/>
+      <x:c r="I261" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" t="n">
+        <x:v>1505</x:v>
+      </x:c>
+      <x:c r="B262" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C262" t="str">
+        <x:v>雷纹玉</x:v>
+      </x:c>
+      <x:c r="D262" t="str">
+        <x:v>res://assets/items/icons_simple/1505.png</x:v>
+      </x:c>
+      <x:c r="E262" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F262" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G262" t="str">
+        <x:v>雷纹玉是玉石一脉的5级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H262" t="str"/>
+      <x:c r="I262" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" t="n">
+        <x:v>1506</x:v>
+      </x:c>
+      <x:c r="B263" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C263" t="str">
+        <x:v>玄冰玉</x:v>
+      </x:c>
+      <x:c r="D263" t="str">
+        <x:v>res://assets/items/icons_simple/1506.png</x:v>
+      </x:c>
+      <x:c r="E263" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F263" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G263" t="str">
+        <x:v>玄冰玉是玉石一脉的6级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H263" t="str"/>
+      <x:c r="I263" t="n">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" t="n">
+        <x:v>1507</x:v>
+      </x:c>
+      <x:c r="B264" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C264" t="str">
+        <x:v>地髓玉</x:v>
+      </x:c>
+      <x:c r="D264" t="str">
+        <x:v>res://assets/items/icons_simple/1507.png</x:v>
+      </x:c>
+      <x:c r="E264" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F264" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G264" t="str">
+        <x:v>地髓玉是玉石一脉的7级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H264" t="str"/>
+      <x:c r="I264" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="n">
+        <x:v>1508</x:v>
+      </x:c>
+      <x:c r="B265" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C265" t="str">
+        <x:v>星辉玉</x:v>
+      </x:c>
+      <x:c r="D265" t="str">
+        <x:v>res://assets/items/icons_simple/1508.png</x:v>
+      </x:c>
+      <x:c r="E265" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F265" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G265" t="str">
+        <x:v>星辉玉是玉石一脉的8级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H265" t="str"/>
+      <x:c r="I265" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="n">
+        <x:v>1509</x:v>
+      </x:c>
+      <x:c r="B266" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C266" t="str">
+        <x:v>龙血玉</x:v>
+      </x:c>
+      <x:c r="D266" t="str">
+        <x:v>res://assets/items/icons_simple/1509.png</x:v>
+      </x:c>
+      <x:c r="E266" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F266" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G266" t="str">
+        <x:v>龙血玉是玉石一脉的9级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H266" t="str"/>
+      <x:c r="I266" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="n">
+        <x:v>1510</x:v>
+      </x:c>
+      <x:c r="B267" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C267" t="str">
+        <x:v>凤栖玉</x:v>
+      </x:c>
+      <x:c r="D267" t="str">
+        <x:v>res://assets/items/icons_simple/1510.png</x:v>
+      </x:c>
+      <x:c r="E267" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F267" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G267" t="str">
+        <x:v>凤栖玉是玉石一脉的10级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H267" t="str"/>
+      <x:c r="I267" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="n">
+        <x:v>1511</x:v>
+      </x:c>
+      <x:c r="B268" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C268" t="str">
+        <x:v>九幽玄玉</x:v>
+      </x:c>
+      <x:c r="D268" t="str">
+        <x:v>res://assets/items/icons_simple/1511.png</x:v>
+      </x:c>
+      <x:c r="E268" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F268" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G268" t="str">
+        <x:v>九幽玄玉是玉石一脉的11级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H268" t="str"/>
+      <x:c r="I268" t="n">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" t="n">
+        <x:v>1512</x:v>
+      </x:c>
+      <x:c r="B269" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C269" t="str">
+        <x:v>扶桑阳玉</x:v>
+      </x:c>
+      <x:c r="D269" t="str">
+        <x:v>res://assets/items/icons_simple/1512.png</x:v>
+      </x:c>
+      <x:c r="E269" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F269" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G269" t="str">
+        <x:v>扶桑阳玉是玉石一脉的12级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H269" t="str"/>
+      <x:c r="I269" t="n">
+        <x:v>40000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="n">
+        <x:v>1513</x:v>
+      </x:c>
+      <x:c r="B270" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C270" t="str">
+        <x:v>建木碧玉</x:v>
+      </x:c>
+      <x:c r="D270" t="str">
+        <x:v>res://assets/items/icons_simple/1513.png</x:v>
+      </x:c>
+      <x:c r="E270" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F270" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G270" t="str">
+        <x:v>建木碧玉是玉石一脉的13级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H270" t="str"/>
+      <x:c r="I270" t="n">
+        <x:v>90000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="B271" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C271" t="str">
+        <x:v>菩提心玉</x:v>
+      </x:c>
+      <x:c r="D271" t="str">
+        <x:v>res://assets/items/icons_simple/1514.png</x:v>
+      </x:c>
+      <x:c r="E271" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F271" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G271" t="str">
+        <x:v>菩提心玉是玉石一脉的14级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H271" t="str"/>
+      <x:c r="I271" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="n">
+        <x:v>1515</x:v>
+      </x:c>
+      <x:c r="B272" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C272" t="str">
+        <x:v>鸿蒙源玉</x:v>
+      </x:c>
+      <x:c r="D272" t="str">
+        <x:v>res://assets/items/icons_simple/1515.png</x:v>
+      </x:c>
+      <x:c r="E272" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F272" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G272" t="str">
+        <x:v>鸿蒙源玉是玉石一脉的15级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H272" t="str"/>
+      <x:c r="I272" t="n">
+        <x:v>450000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="n">
+        <x:v>1516</x:v>
+      </x:c>
+      <x:c r="B273" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C273" t="str">
+        <x:v>太初神玉</x:v>
+      </x:c>
+      <x:c r="D273" t="str">
+        <x:v>res://assets/items/icons_simple/1516.png</x:v>
+      </x:c>
+      <x:c r="E273" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F273" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G273" t="str">
+        <x:v>太初神玉是玉石一脉的16级材料，可用于对应层次的修真制作。</x:v>
+      </x:c>
+      <x:c r="H273" t="str"/>
+      <x:c r="I273" t="n">
+        <x:v>1000000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -17569,6 +19744,1206 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="4" t="n">
+        <x:v>28101</x:v>
+      </x:c>
+      <x:c r="B209" s="4"/>
+      <x:c r="C209" s="4" t="str">
+        <x:v>松露养元散</x:v>
+      </x:c>
+      <x:c r="D209" s="4"/>
+      <x:c r="E209" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="str">
+        <x:v>松露养元散以松露灵脂、青鳞灵鱼、雾芽草合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G209" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H209" s="4"/>
+      <x:c r="I209" s="4"/>
+      <x:c r="J209" s="4"/>
+      <x:c r="K209" s="4"/>
+      <x:c r="L209" s="4"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="4" t="n">
+        <x:v>28102</x:v>
+      </x:c>
+      <x:c r="B210" s="4"/>
+      <x:c r="C210" s="4" t="str">
+        <x:v>银鳞抱元丸</x:v>
+      </x:c>
+      <x:c r="D210" s="4"/>
+      <x:c r="E210" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F210" s="4" t="str">
+        <x:v>银鳞抱元丸以银须鲫、青络花合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G210" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H210" s="4"/>
+      <x:c r="I210" s="4"/>
+      <x:c r="J210" s="4"/>
+      <x:c r="K210" s="4"/>
+      <x:c r="L210" s="4"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="4" t="n">
+        <x:v>28103</x:v>
+      </x:c>
+      <x:c r="B211" s="4"/>
+      <x:c r="C211" s="4" t="str">
+        <x:v>月桂玉露丹</x:v>
+      </x:c>
+      <x:c r="D211" s="4"/>
+      <x:c r="E211" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="str">
+        <x:v>月桂玉露丹以月桂凝脂、月纹鳜、玉壶露合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G211" s="4" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H211" s="4"/>
+      <x:c r="I211" s="4"/>
+      <x:c r="J211" s="4"/>
+      <x:c r="K211" s="4"/>
+      <x:c r="L211" s="4"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="4" t="n">
+        <x:v>28104</x:v>
+      </x:c>
+      <x:c r="B212" s="4"/>
+      <x:c r="C212" s="4" t="str">
+        <x:v>雷脂雪魄丸</x:v>
+      </x:c>
+      <x:c r="D212" s="4"/>
+      <x:c r="E212" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F212" s="4" t="str">
+        <x:v>雷脂雪魄丸以桃木雷脂、雷鳍鲶、雪魄莲合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G212" s="4" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H212" s="4"/>
+      <x:c r="I212" s="4"/>
+      <x:c r="J212" s="4"/>
+      <x:c r="K212" s="4"/>
+      <x:c r="L212" s="4"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="4" t="n">
+        <x:v>28105</x:v>
+      </x:c>
+      <x:c r="B213" s="4"/>
+      <x:c r="C213" s="4" t="str">
+        <x:v>沉香青冥丹</x:v>
+      </x:c>
+      <x:c r="D213" s="4"/>
+      <x:c r="E213" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F213" s="4" t="str">
+        <x:v>沉香青冥丹以沉香地髓、地脉鳅、苍梧藤合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G213" s="4" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="H213" s="4"/>
+      <x:c r="I213" s="4"/>
+      <x:c r="J213" s="4"/>
+      <x:c r="K213" s="4"/>
+      <x:c r="L213" s="4"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="4" t="n">
+        <x:v>28106</x:v>
+      </x:c>
+      <x:c r="B214" s="4"/>
+      <x:c r="C214" s="4" t="str">
+        <x:v>星脂霆元丹</x:v>
+      </x:c>
+      <x:c r="D214" s="4"/>
+      <x:c r="E214" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F214" s="4" t="str">
+        <x:v>星脂霆元丹以紫檀星脂、星斑鲷、霆光竹合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G214" s="4" t="n">
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="H214" s="4"/>
+      <x:c r="I214" s="4"/>
+      <x:c r="J214" s="4"/>
+      <x:c r="K214" s="4"/>
+      <x:c r="L214" s="4"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="4" t="n">
+        <x:v>28107</x:v>
+      </x:c>
+      <x:c r="B215" s="4"/>
+      <x:c r="C215" s="4" t="str">
+        <x:v>凤鲤星华丹</x:v>
+      </x:c>
+      <x:c r="D215" s="4"/>
+      <x:c r="E215" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F215" s="4" t="str">
+        <x:v>凤鲤星华丹以凤栖香脂、凤尾锦鲤、星坠蕊合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G215" s="4" t="n">
+        <x:v>23832</x:v>
+      </x:c>
+      <x:c r="H215" s="4"/>
+      <x:c r="I215" s="4"/>
+      <x:c r="J215" s="4"/>
+      <x:c r="K215" s="4"/>
+      <x:c r="L215" s="4"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="4" t="n">
+        <x:v>28108</x:v>
+      </x:c>
+      <x:c r="B216" s="4"/>
+      <x:c r="C216" s="4" t="str">
+        <x:v>扶桑九转丹</x:v>
+      </x:c>
+      <x:c r="D216" s="4"/>
+      <x:c r="E216" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F216" s="4" t="str">
+        <x:v>扶桑九转丹以扶桑日脂、扶桑金鲤、九曲槲合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G216" s="4" t="n">
+        <x:v>122681</x:v>
+      </x:c>
+      <x:c r="H216" s="4"/>
+      <x:c r="I216" s="4"/>
+      <x:c r="J216" s="4"/>
+      <x:c r="K216" s="4"/>
+      <x:c r="L216" s="4"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="4" t="n">
+        <x:v>28109</x:v>
+      </x:c>
+      <x:c r="B217" s="4"/>
+      <x:c r="C217" s="4" t="str">
+        <x:v>菩提龙元丹</x:v>
+      </x:c>
+      <x:c r="D217" s="4"/>
+      <x:c r="E217" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F217" s="4" t="str">
+        <x:v>菩提龙元丹以菩提心脂、菩提慧鱼、螭涎兰合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G217" s="4" t="n">
+        <x:v>633683</x:v>
+      </x:c>
+      <x:c r="H217" s="4"/>
+      <x:c r="I217" s="4"/>
+      <x:c r="J217" s="4"/>
+      <x:c r="K217" s="4"/>
+      <x:c r="L217" s="4"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="4" t="n">
+        <x:v>28110</x:v>
+      </x:c>
+      <x:c r="B218" s="4"/>
+      <x:c r="C218" s="4" t="str">
+        <x:v>太初造化丹</x:v>
+      </x:c>
+      <x:c r="D218" s="4"/>
+      <x:c r="E218" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F218" s="4" t="str">
+        <x:v>太初造化丹以太初神脂、太初神鲲、太初道种合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G218" s="4" t="n">
+        <x:v>3285215</x:v>
+      </x:c>
+      <x:c r="H218" s="4"/>
+      <x:c r="I218" s="4"/>
+      <x:c r="J218" s="4"/>
+      <x:c r="K218" s="4"/>
+      <x:c r="L218" s="4"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="4" t="n">
+        <x:v>28111</x:v>
+      </x:c>
+      <x:c r="B219" s="4"/>
+      <x:c r="C219" s="4" t="str">
+        <x:v>松露青果酿</x:v>
+      </x:c>
+      <x:c r="D219" s="4"/>
+      <x:c r="E219" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F219" s="4" t="str">
+        <x:v>松露青果酿以松露灵脂、山青果合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G219" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H219" s="4"/>
+      <x:c r="I219" s="4"/>
+      <x:c r="J219" s="4"/>
+      <x:c r="K219" s="4"/>
+      <x:c r="L219" s="4"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="4" t="n">
+        <x:v>28112</x:v>
+      </x:c>
+      <x:c r="B220" s="4"/>
+      <x:c r="C220" s="4" t="str">
+        <x:v>银须青禾酒</x:v>
+      </x:c>
+      <x:c r="D220" s="4"/>
+      <x:c r="E220" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F220" s="4" t="str">
+        <x:v>银须青禾酒以银须鲫、青禾米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G220" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H220" s="4"/>
+      <x:c r="I220" s="4"/>
+      <x:c r="J220" s="4"/>
+      <x:c r="K220" s="4"/>
+      <x:c r="L220" s="4"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="4" t="n">
+        <x:v>28113</x:v>
+      </x:c>
+      <x:c r="B221" s="4"/>
+      <x:c r="C221" s="4" t="str">
+        <x:v>赤枫金铃酿</x:v>
+      </x:c>
+      <x:c r="D221" s="4"/>
+      <x:c r="E221" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F221" s="4" t="str">
+        <x:v>赤枫金铃酿以赤枫脂、赤尾鲤、金铃果合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G221" s="4" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H221" s="4"/>
+      <x:c r="I221" s="4"/>
+      <x:c r="J221" s="4"/>
+      <x:c r="K221" s="4"/>
+      <x:c r="L221" s="4"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="4" t="n">
+        <x:v>28114</x:v>
+      </x:c>
+      <x:c r="B222" s="4"/>
+      <x:c r="C222" s="4" t="str">
+        <x:v>雷脂雪纹酒</x:v>
+      </x:c>
+      <x:c r="D222" s="4"/>
+      <x:c r="E222" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F222" s="4" t="str">
+        <x:v>雷脂雪纹酒以桃木雷脂、雷鳍鲶、雪纹米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G222" s="4" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H222" s="4"/>
+      <x:c r="I222" s="4"/>
+      <x:c r="J222" s="4"/>
+      <x:c r="K222" s="4"/>
+      <x:c r="L222" s="4"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="4" t="n">
+        <x:v>28115</x:v>
+      </x:c>
+      <x:c r="B223" s="4"/>
+      <x:c r="C223" s="4" t="str">
+        <x:v>冰魄苍梧酿</x:v>
+      </x:c>
+      <x:c r="D223" s="4"/>
+      <x:c r="E223" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F223" s="4" t="str">
+        <x:v>冰魄苍梧酿以冰梧寒脂、冰魄鲑、苍梧子合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G223" s="4" t="n">
+        <x:v>2851</x:v>
+      </x:c>
+      <x:c r="H223" s="4"/>
+      <x:c r="I223" s="4"/>
+      <x:c r="J223" s="4"/>
+      <x:c r="K223" s="4"/>
+      <x:c r="L223" s="4"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="4" t="n">
+        <x:v>28116</x:v>
+      </x:c>
+      <x:c r="B224" s="4"/>
+      <x:c r="C224" s="4" t="str">
+        <x:v>星脂雷芒酒</x:v>
+      </x:c>
+      <x:c r="D224" s="4"/>
+      <x:c r="E224" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F224" s="4" t="str">
+        <x:v>星脂雷芒酒以紫檀星脂、星斑鲷、雷芒米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G224" s="4" t="n">
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="H224" s="4"/>
+      <x:c r="I224" s="4"/>
+      <x:c r="J224" s="4"/>
+      <x:c r="K224" s="4"/>
+      <x:c r="L224" s="4"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="4" t="n">
+        <x:v>28117</x:v>
+      </x:c>
+      <x:c r="B225" s="4"/>
+      <x:c r="C225" s="4" t="str">
+        <x:v>龙血星子酿</x:v>
+      </x:c>
+      <x:c r="D225" s="4"/>
+      <x:c r="E225" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F225" s="4" t="str">
+        <x:v>龙血星子酿以龙血木脂、龙须鲤、星子米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G225" s="4" t="n">
+        <x:v>13032</x:v>
+      </x:c>
+      <x:c r="H225" s="4"/>
+      <x:c r="I225" s="4"/>
+      <x:c r="J225" s="4"/>
+      <x:c r="K225" s="4"/>
+      <x:c r="L225" s="4"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="4" t="n">
+        <x:v>28118</x:v>
+      </x:c>
+      <x:c r="B226" s="4"/>
+      <x:c r="C226" s="4" t="str">
+        <x:v>九幽九曲醪</x:v>
+      </x:c>
+      <x:c r="D226" s="4"/>
+      <x:c r="E226" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F226" s="4" t="str">
+        <x:v>九幽九曲醪以九幽玄脂、九幽玄鱼、九曲米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G226" s="4" t="n">
+        <x:v>69881</x:v>
+      </x:c>
+      <x:c r="H226" s="4"/>
+      <x:c r="I226" s="4"/>
+      <x:c r="J226" s="4"/>
+      <x:c r="K226" s="4"/>
+      <x:c r="L226" s="4"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="4" t="n">
+        <x:v>28119</x:v>
+      </x:c>
+      <x:c r="B227" s="4"/>
+      <x:c r="C227" s="4" t="str">
+        <x:v>建木龙牙酿</x:v>
+      </x:c>
+      <x:c r="D227" s="4"/>
+      <x:c r="E227" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F227" s="4" t="str">
+        <x:v>建木龙牙酿以建木玉脂、建木游龙、龙牙米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G227" s="4" t="n">
+        <x:v>369683</x:v>
+      </x:c>
+      <x:c r="H227" s="4"/>
+      <x:c r="I227" s="4"/>
+      <x:c r="J227" s="4"/>
+      <x:c r="K227" s="4"/>
+      <x:c r="L227" s="4"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="4" t="n">
+        <x:v>28120</x:v>
+      </x:c>
+      <x:c r="B228" s="4"/>
+      <x:c r="C228" s="4" t="str">
+        <x:v>鸿蒙玄粟酒</x:v>
+      </x:c>
+      <x:c r="D228" s="4"/>
+      <x:c r="E228" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F228" s="4" t="str">
+        <x:v>鸿蒙玄粟酒以鸿蒙源脂、鸿蒙鲲苗、太初玄粟合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G228" s="4" t="n">
+        <x:v>1965215</x:v>
+      </x:c>
+      <x:c r="H228" s="4"/>
+      <x:c r="I228" s="4"/>
+      <x:c r="J228" s="4"/>
+      <x:c r="K228" s="4"/>
+      <x:c r="L228" s="4"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="4" t="n">
+        <x:v>28121</x:v>
+      </x:c>
+      <x:c r="B229" s="4"/>
+      <x:c r="C229" s="4" t="str">
+        <x:v>青枝铜骨剑</x:v>
+      </x:c>
+      <x:c r="D229" s="4"/>
+      <x:c r="E229" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F229" s="4" t="str">
+        <x:v>青枝铜骨剑以青灵枝、赤髓铜合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G229" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H229" s="4"/>
+      <x:c r="I229" s="4"/>
+      <x:c r="J229" s="4"/>
+      <x:c r="K229" s="4"/>
+      <x:c r="L229" s="4"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="4" t="n">
+        <x:v>28122</x:v>
+      </x:c>
+      <x:c r="B230" s="4"/>
+      <x:c r="C230" s="4" t="str">
+        <x:v>云木乌铁刀</x:v>
+      </x:c>
+      <x:c r="D230" s="4"/>
+      <x:c r="E230" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F230" s="4" t="str">
+        <x:v>云木乌铁刀以云纹木、乌纹铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G230" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H230" s="4"/>
+      <x:c r="I230" s="4"/>
+      <x:c r="J230" s="4"/>
+      <x:c r="K230" s="4"/>
+      <x:c r="L230" s="4"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="4" t="n">
+        <x:v>28123</x:v>
+      </x:c>
+      <x:c r="B231" s="4"/>
+      <x:c r="C231" s="4" t="str">
+        <x:v>月桂白金杖</x:v>
+      </x:c>
+      <x:c r="D231" s="4"/>
+      <x:c r="E231" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F231" s="4" t="str">
+        <x:v>月桂白金杖以月桂灵木、月华玉、太白金母合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G231" s="4" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H231" s="4"/>
+      <x:c r="I231" s="4"/>
+      <x:c r="J231" s="4"/>
+      <x:c r="K231" s="4"/>
+      <x:c r="L231" s="4"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="4" t="n">
+        <x:v>28124</x:v>
+      </x:c>
+      <x:c r="B232" s="4"/>
+      <x:c r="C232" s="4" t="str">
+        <x:v>雷木玄冰枪</x:v>
+      </x:c>
+      <x:c r="D232" s="4"/>
+      <x:c r="E232" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F232" s="4" t="str">
+        <x:v>雷木玄冰枪以雷击桃木、雷纹玉、玄冰陨铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G232" s="4" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H232" s="4"/>
+      <x:c r="I232" s="4"/>
+      <x:c r="J232" s="4"/>
+      <x:c r="K232" s="4"/>
+      <x:c r="L232" s="4"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="4" t="n">
+        <x:v>28125</x:v>
+      </x:c>
+      <x:c r="B233" s="4"/>
+      <x:c r="C233" s="4" t="str">
+        <x:v>沉香青罡印</x:v>
+      </x:c>
+      <x:c r="D233" s="4"/>
+      <x:c r="E233" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F233" s="4" t="str">
+        <x:v>沉香青罡印以地脉沉香、地髓玉、青罡玉合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G233" s="4" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="H233" s="4"/>
+      <x:c r="I233" s="4"/>
+      <x:c r="J233" s="4"/>
+      <x:c r="K233" s="4"/>
+      <x:c r="L233" s="4"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="4" t="n">
+        <x:v>28126</x:v>
+      </x:c>
+      <x:c r="B234" s="4"/>
+      <x:c r="C234" s="4" t="str">
+        <x:v>紫檀雷极轮</x:v>
+      </x:c>
+      <x:c r="D234" s="4"/>
+      <x:c r="E234" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F234" s="4" t="str">
+        <x:v>紫檀雷极轮以星辉紫檀、星辉玉、雷极砂合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G234" s="4" t="n">
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="H234" s="4"/>
+      <x:c r="I234" s="4"/>
+      <x:c r="J234" s="4"/>
+      <x:c r="K234" s="4"/>
+      <x:c r="L234" s="4"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="4" t="n">
+        <x:v>28127</x:v>
+      </x:c>
+      <x:c r="B235" s="4"/>
+      <x:c r="C235" s="4" t="str">
+        <x:v>凤木星陨弓</x:v>
+      </x:c>
+      <x:c r="D235" s="4"/>
+      <x:c r="E235" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F235" s="4" t="str">
+        <x:v>凤木星陨弓以凤栖神木、凤栖玉、星陨铁核合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G235" s="4" t="n">
+        <x:v>23832</x:v>
+      </x:c>
+      <x:c r="H235" s="4"/>
+      <x:c r="I235" s="4"/>
+      <x:c r="J235" s="4"/>
+      <x:c r="K235" s="4"/>
+      <x:c r="L235" s="4"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="4" t="n">
+        <x:v>28128</x:v>
+      </x:c>
+      <x:c r="B236" s="4"/>
+      <x:c r="C236" s="4" t="str">
+        <x:v>扶桑九幽戟</x:v>
+      </x:c>
+      <x:c r="D236" s="4"/>
+      <x:c r="E236" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F236" s="4" t="str">
+        <x:v>扶桑九幽戟以扶桑阳木、扶桑阳玉、九幽沉铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G236" s="4" t="n">
+        <x:v>122681</x:v>
+      </x:c>
+      <x:c r="H236" s="4"/>
+      <x:c r="I236" s="4"/>
+      <x:c r="J236" s="4"/>
+      <x:c r="K236" s="4"/>
+      <x:c r="L236" s="4"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="4" t="n">
+        <x:v>28129</x:v>
+      </x:c>
+      <x:c r="B237" s="4"/>
+      <x:c r="C237" s="4" t="str">
+        <x:v>菩提月魄钟</x:v>
+      </x:c>
+      <x:c r="D237" s="4"/>
+      <x:c r="E237" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F237" s="4" t="str">
+        <x:v>菩提月魄钟以菩提道木、菩提心玉、月魄寒玉合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G237" s="4" t="n">
+        <x:v>633683</x:v>
+      </x:c>
+      <x:c r="H237" s="4"/>
+      <x:c r="I237" s="4"/>
+      <x:c r="J237" s="4"/>
+      <x:c r="K237" s="4"/>
+      <x:c r="L237" s="4"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="4" t="n">
+        <x:v>28130</x:v>
+      </x:c>
+      <x:c r="B238" s="4"/>
+      <x:c r="C238" s="4" t="str">
+        <x:v>世界树开天斧</x:v>
+      </x:c>
+      <x:c r="D238" s="4"/>
+      <x:c r="E238" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F238" s="4" t="str">
+        <x:v>世界树开天斧以世界树心、太初神玉、鸿蒙母晶合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G238" s="4" t="n">
+        <x:v>3285215</x:v>
+      </x:c>
+      <x:c r="H238" s="4"/>
+      <x:c r="I238" s="4"/>
+      <x:c r="J238" s="4"/>
+      <x:c r="K238" s="4"/>
+      <x:c r="L238" s="4"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="4" t="n">
+        <x:v>28131</x:v>
+      </x:c>
+      <x:c r="B239" s="4"/>
+      <x:c r="C239" s="4" t="str">
+        <x:v>清珠岚障阵</x:v>
+      </x:c>
+      <x:c r="D239" s="4"/>
+      <x:c r="E239" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F239" s="4" t="str">
+        <x:v>清珠岚障阵以清水灵珠、青白玉、清岚障图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G239" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H239" s="4"/>
+      <x:c r="I239" s="4"/>
+      <x:c r="J239" s="4"/>
+      <x:c r="K239" s="4"/>
+      <x:c r="L239" s="4"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="4" t="n">
+        <x:v>28132</x:v>
+      </x:c>
+      <x:c r="B240" s="4"/>
+      <x:c r="C240" s="4" t="str">
+        <x:v>云玉聚炁阵</x:v>
+      </x:c>
+      <x:c r="D240" s="4"/>
+      <x:c r="E240" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F240" s="4" t="str">
+        <x:v>云玉聚炁阵以青波珠、云纹玉、引星聚炁图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G240" s="4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H240" s="4"/>
+      <x:c r="I240" s="4"/>
+      <x:c r="J240" s="4"/>
+      <x:c r="K240" s="4"/>
+      <x:c r="L240" s="4"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="4" t="n">
+        <x:v>28133</x:v>
+      </x:c>
+      <x:c r="B241" s="4"/>
+      <x:c r="C241" s="4" t="str">
+        <x:v>月珠锁灵阵</x:v>
+      </x:c>
+      <x:c r="D241" s="4"/>
+      <x:c r="E241" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F241" s="4" t="str">
+        <x:v>月珠锁灵阵以赤潮珠、月华珠、赤霞玉、三垣锁灵图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G241" s="4" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H241" s="4"/>
+      <x:c r="I241" s="4"/>
+      <x:c r="J241" s="4"/>
+      <x:c r="K241" s="4"/>
+      <x:c r="L241" s="4"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="4" t="n">
+        <x:v>28134</x:v>
+      </x:c>
+      <x:c r="B242" s="4"/>
+      <x:c r="C242" s="4" t="str">
+        <x:v>雷珠寒光阵</x:v>
+      </x:c>
+      <x:c r="D242" s="4"/>
+      <x:c r="E242" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F242" s="4" t="str">
+        <x:v>雷珠寒光阵以雷鸣珠、雷纹玉、四渎寒图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G242" s="4" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H242" s="4"/>
+      <x:c r="I242" s="4"/>
+      <x:c r="J242" s="4"/>
+      <x:c r="K242" s="4"/>
+      <x:c r="L242" s="4"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="4" t="n">
+        <x:v>28135</x:v>
+      </x:c>
+      <x:c r="B243" s="4"/>
+      <x:c r="C243" s="4" t="str">
+        <x:v>地珠载岳阵</x:v>
+      </x:c>
+      <x:c r="D243" s="4"/>
+      <x:c r="E243" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F243" s="4" t="str">
+        <x:v>地珠载岳阵以玄冰珠、地泉珠、玄冰玉、玄龟载岳图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G243" s="4" t="n">
+        <x:v>1895</x:v>
+      </x:c>
+      <x:c r="H243" s="4"/>
+      <x:c r="I243" s="4"/>
+      <x:c r="J243" s="4"/>
+      <x:c r="K243" s="4"/>
+      <x:c r="L243" s="4"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="4" t="n">
+        <x:v>28136</x:v>
+      </x:c>
+      <x:c r="B244" s="4"/>
+      <x:c r="C244" s="4" t="str">
+        <x:v>星珠九霄阵</x:v>
+      </x:c>
+      <x:c r="D244" s="4"/>
+      <x:c r="E244" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F244" s="4" t="str">
+        <x:v>星珠九霄阵以星澜珠、星辉玉、九霄雷篆图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G244" s="4" t="n">
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="H244" s="4"/>
+      <x:c r="I244" s="4"/>
+      <x:c r="J244" s="4"/>
+      <x:c r="K244" s="4"/>
+      <x:c r="L244" s="4"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="4" t="n">
+        <x:v>28137</x:v>
+      </x:c>
+      <x:c r="B245" s="4"/>
+      <x:c r="C245" s="4" t="str">
+        <x:v>凤珠星罗阵</x:v>
+      </x:c>
+      <x:c r="D245" s="4"/>
+      <x:c r="E245" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F245" s="4" t="str">
+        <x:v>凤珠星罗阵以龙涎珠、凤泪珠、龙血玉、星罗天盘图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G245" s="4" t="n">
+        <x:v>22632</x:v>
+      </x:c>
+      <x:c r="H245" s="4"/>
+      <x:c r="I245" s="4"/>
+      <x:c r="J245" s="4"/>
+      <x:c r="K245" s="4"/>
+      <x:c r="L245" s="4"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="4" t="n">
+        <x:v>28138</x:v>
+      </x:c>
+      <x:c r="B246" s="4"/>
+      <x:c r="C246" s="4" t="str">
+        <x:v>日珠续命阵</x:v>
+      </x:c>
+      <x:c r="D246" s="4"/>
+      <x:c r="E246" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F246" s="4" t="str">
+        <x:v>日珠续命阵以九幽玄珠、扶桑日珠、九幽玄玉、九幽续命图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G246" s="4" t="n">
+        <x:v>117881</x:v>
+      </x:c>
+      <x:c r="H246" s="4"/>
+      <x:c r="I246" s="4"/>
+      <x:c r="J246" s="4"/>
+      <x:c r="K246" s="4"/>
+      <x:c r="L246" s="4"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="4" t="n">
+        <x:v>28139</x:v>
+      </x:c>
+      <x:c r="B247" s="4"/>
+      <x:c r="C247" s="4" t="str">
+        <x:v>心珠御龙阵</x:v>
+      </x:c>
+      <x:c r="D247" s="4"/>
+      <x:c r="E247" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F247" s="4" t="str">
+        <x:v>心珠御龙阵以建木碧珠、菩提心珠、建木碧玉、苍龙御天图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G247" s="4" t="n">
+        <x:v>609683</x:v>
+      </x:c>
+      <x:c r="H247" s="4"/>
+      <x:c r="I247" s="4"/>
+      <x:c r="J247" s="4"/>
+      <x:c r="K247" s="4"/>
+      <x:c r="L247" s="4"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="4" t="n">
+        <x:v>28140</x:v>
+      </x:c>
+      <x:c r="B248" s="4"/>
+      <x:c r="C248" s="4" t="str">
+        <x:v>太初万象阵</x:v>
+      </x:c>
+      <x:c r="D248" s="4"/>
+      <x:c r="E248" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F248" s="4" t="str">
+        <x:v>太初万象阵以鸿蒙源珠、太初神珠、鸿蒙源玉、太一归元图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G248" s="4" t="n">
+        <x:v>3165215</x:v>
+      </x:c>
+      <x:c r="H248" s="4"/>
+      <x:c r="I248" s="4"/>
+      <x:c r="J248" s="4"/>
+      <x:c r="K248" s="4"/>
+      <x:c r="L248" s="4"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="4" t="n">
+        <x:v>28141</x:v>
+      </x:c>
+      <x:c r="B249" s="4"/>
+      <x:c r="C249" s="4" t="str">
+        <x:v>青枝镇煞符</x:v>
+      </x:c>
+      <x:c r="D249" s="4"/>
+      <x:c r="E249" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F249" s="4" t="str">
+        <x:v>青枝镇煞符以青灵枝、山豕血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G249" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H249" s="4"/>
+      <x:c r="I249" s="4"/>
+      <x:c r="J249" s="4"/>
+      <x:c r="K249" s="4"/>
+      <x:c r="L249" s="4"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="4" t="n">
+        <x:v>28142</x:v>
+      </x:c>
+      <x:c r="B250" s="4"/>
+      <x:c r="C250" s="4" t="str">
+        <x:v>青檀净心符</x:v>
+      </x:c>
+      <x:c r="D250" s="4"/>
+      <x:c r="E250" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F250" s="4" t="str">
+        <x:v>青檀净心符以青檀脂、云鹿灵血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G250" s="4" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H250" s="4"/>
+      <x:c r="I250" s="4"/>
+      <x:c r="J250" s="4"/>
+      <x:c r="K250" s="4"/>
+      <x:c r="L250" s="4"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="4" t="n">
+        <x:v>28143</x:v>
+      </x:c>
+      <x:c r="B251" s="4"/>
+      <x:c r="C251" s="4" t="str">
+        <x:v>赤霞金身符</x:v>
+      </x:c>
+      <x:c r="D251" s="4"/>
+      <x:c r="E251" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F251" s="4" t="str">
+        <x:v>赤霞金身符以赤霞杉、月桂凝脂、金蟾髓合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G251" s="4" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H251" s="4"/>
+      <x:c r="I251" s="4"/>
+      <x:c r="J251" s="4"/>
+      <x:c r="K251" s="4"/>
+      <x:c r="L251" s="4"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="4" t="n">
+        <x:v>28144</x:v>
+      </x:c>
+      <x:c r="B252" s="4"/>
+      <x:c r="C252" s="4" t="str">
+        <x:v>雷木寒霜符</x:v>
+      </x:c>
+      <x:c r="D252" s="4"/>
+      <x:c r="E252" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F252" s="4" t="str">
+        <x:v>雷木寒霜符以雷击桃木、桃木雷脂、冰蛇寒血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G252" s="4" t="n">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="H252" s="4"/>
+      <x:c r="I252" s="4"/>
+      <x:c r="J252" s="4"/>
+      <x:c r="K252" s="4"/>
+      <x:c r="L252" s="4"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="4" t="n">
+        <x:v>28145</x:v>
+      </x:c>
+      <x:c r="B253" s="4"/>
+      <x:c r="C253" s="4" t="str">
+        <x:v>冰梧青鸾符</x:v>
+      </x:c>
+      <x:c r="D253" s="4"/>
+      <x:c r="E253" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F253" s="4" t="str">
+        <x:v>冰梧青鸾符以玄冰梧桐、沉香地髓、青鸾碧血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G253" s="4" t="n">
+        <x:v>3331</x:v>
+      </x:c>
+      <x:c r="H253" s="4"/>
+      <x:c r="I253" s="4"/>
+      <x:c r="J253" s="4"/>
+      <x:c r="K253" s="4"/>
+      <x:c r="L253" s="4"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="4" t="n">
+        <x:v>28146</x:v>
+      </x:c>
+      <x:c r="B254" s="4"/>
+      <x:c r="C254" s="4" t="str">
+        <x:v>紫檀雷鹏符</x:v>
+      </x:c>
+      <x:c r="D254" s="4"/>
+      <x:c r="E254" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F254" s="4" t="str">
+        <x:v>紫檀雷鹏符以星辉紫檀、紫檀星脂、雷鹏紫血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G254" s="4" t="n">
+        <x:v>8716</x:v>
+      </x:c>
+      <x:c r="H254" s="4"/>
+      <x:c r="I254" s="4"/>
+      <x:c r="J254" s="4"/>
+      <x:c r="K254" s="4"/>
+      <x:c r="L254" s="4"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="4" t="n">
+        <x:v>28147</x:v>
+      </x:c>
+      <x:c r="B255" s="4"/>
+      <x:c r="C255" s="4" t="str">
+        <x:v>龙血星狼符</x:v>
+      </x:c>
+      <x:c r="D255" s="4"/>
+      <x:c r="E255" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F255" s="4" t="str">
+        <x:v>龙血星狼符以龙血古木、凤栖香脂、星狼银血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G255" s="4" t="n">
+        <x:v>43268</x:v>
+      </x:c>
+      <x:c r="H255" s="4"/>
+      <x:c r="I255" s="4"/>
+      <x:c r="J255" s="4"/>
+      <x:c r="K255" s="4"/>
+      <x:c r="L255" s="4"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="4" t="n">
+        <x:v>28148</x:v>
+      </x:c>
+      <x:c r="B256" s="4"/>
+      <x:c r="C256" s="4" t="str">
+        <x:v>九幽九命符</x:v>
+      </x:c>
+      <x:c r="D256" s="4"/>
+      <x:c r="E256" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F256" s="4" t="str">
+        <x:v>九幽九命符以九幽冥木、扶桑日脂、九命猫血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G256" s="4" t="n">
+        <x:v>239339</x:v>
+      </x:c>
+      <x:c r="H256" s="4"/>
+      <x:c r="I256" s="4"/>
+      <x:c r="J256" s="4"/>
+      <x:c r="K256" s="4"/>
+      <x:c r="L256" s="4"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="4" t="n">
+        <x:v>28149</x:v>
+      </x:c>
+      <x:c r="B257" s="4"/>
+      <x:c r="C257" s="4" t="str">
+        <x:v>建木龙血符</x:v>
+      </x:c>
+      <x:c r="D257" s="4"/>
+      <x:c r="E257" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F257" s="4" t="str">
+        <x:v>建木龙血符以建木灵芯、菩提心脂、苍龙真血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G257" s="4" t="n">
+        <x:v>1325698</x:v>
+      </x:c>
+      <x:c r="H257" s="4"/>
+      <x:c r="I257" s="4"/>
+      <x:c r="J257" s="4"/>
+      <x:c r="K257" s="4"/>
+      <x:c r="L257" s="4"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="4" t="n">
+        <x:v>28150</x:v>
+      </x:c>
+      <x:c r="B258" s="4"/>
+      <x:c r="C258" s="4" t="str">
+        <x:v>鸿蒙太古符</x:v>
+      </x:c>
+      <x:c r="D258" s="4"/>
+      <x:c r="E258" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F258" s="4" t="str">
+        <x:v>鸿蒙太古符以鸿蒙祖木、太初神脂、太古源血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</x:v>
+      </x:c>
+      <x:c r="G258" s="4" t="n">
+        <x:v>7371541</x:v>
+      </x:c>
+      <x:c r="H258" s="4"/>
+      <x:c r="I258" s="4"/>
+      <x:c r="J258" s="4"/>
+      <x:c r="K258" s="4"/>
+      <x:c r="L258" s="4"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -19084,6 +22459,254 @@
       <x:c r="I44" s="3" t="n">
         <x:v>600</x:v>
       </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="B45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>普通灵石</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>res://assets/items/icons_simple/1601.png</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>普通灵石，点击使用可获得1灵石。</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>1602</x:v>
+      </x:c>
+      <x:c r="B46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>中品灵石</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>res://assets/items/icons_simple/1602.png</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>中品灵石，点击使用可获得5灵石。</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>1603</x:v>
+      </x:c>
+      <x:c r="B47" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>上品灵石</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>res://assets/items/icons_simple/1603.png</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>上品灵石，点击使用可获得15灵石。</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>1604</x:v>
+      </x:c>
+      <x:c r="B48" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>极品灵石</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>res://assets/items/icons_simple/1604.png</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>极品灵石，点击使用可获得40灵石。</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+      <x:c r="G49"/>
+      <x:c r="H49"/>
+      <x:c r="I49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+      <x:c r="G50"/>
+      <x:c r="H50"/>
+      <x:c r="I50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+      <x:c r="I52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
+      <x:c r="F53"/>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54"/>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55"/>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+      <x:c r="I55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56"/>
+      <x:c r="B56"/>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56"/>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+      <x:c r="I56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57"/>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
+      <x:c r="I57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58"/>
+      <x:c r="G58"/>
+      <x:c r="H58"/>
+      <x:c r="I58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59"/>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
+      <x:c r="I59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60"/>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
+      <x:c r="E60"/>
+      <x:c r="F60"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+      <x:c r="I60"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23970,6 +27593,1638 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>23001</x:v>
+      </x:c>
+      <x:c r="B98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>青篱灵木园</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>res://assets/items/icons_simple/23001.png</x:v>
+      </x:c>
+      <x:c r="E98" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H98" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>青篱灵木园可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J98"/>
+      <x:c r="K98" t="str">
+        <x:v>1101:7;1201:3</x:v>
+      </x:c>
+      <x:c r="L98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>24001</x:v>
+      </x:c>
+      <x:c r="B99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>清波灵潭</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>res://assets/items/icons_simple/24001.png</x:v>
+      </x:c>
+      <x:c r="E99" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H99" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>清波灵潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J99"/>
+      <x:c r="K99" t="str">
+        <x:v>1301:7;1401:3</x:v>
+      </x:c>
+      <x:c r="L99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>25001</x:v>
+      </x:c>
+      <x:c r="B100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>浅层灵石矿脉</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>res://assets/items/icons_simple/25001.png</x:v>
+      </x:c>
+      <x:c r="E100" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H100" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>浅层灵石矿脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J100"/>
+      <x:c r="K100" t="str">
+        <x:v>1501:9500;1601:500</x:v>
+      </x:c>
+      <x:c r="L100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>23002</x:v>
+      </x:c>
+      <x:c r="B101" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>云露木圃</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>res://assets/items/icons_simple/23002.png</x:v>
+      </x:c>
+      <x:c r="E101" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H101" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>云露木圃可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J101"/>
+      <x:c r="K101" t="str">
+        <x:v>1101:686;1201:294;1102:14;1202:6</x:v>
+      </x:c>
+      <x:c r="L101" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>24002</x:v>
+      </x:c>
+      <x:c r="B102" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>青涟鱼池</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>res://assets/items/icons_simple/24002.png</x:v>
+      </x:c>
+      <x:c r="E102" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H102" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>青涟鱼池可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J102"/>
+      <x:c r="K102" t="str">
+        <x:v>1301:686;1401:294;1302:14;1402:6</x:v>
+      </x:c>
+      <x:c r="L102" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>25002</x:v>
+      </x:c>
+      <x:c r="B103" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>青岩矿脉</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>res://assets/items/icons_simple/25002.png</x:v>
+      </x:c>
+      <x:c r="E103" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H103" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>青岩矿脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J103"/>
+      <x:c r="K103" t="str">
+        <x:v>1501:9310;1502:190;1601:500</x:v>
+      </x:c>
+      <x:c r="L103" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>23003</x:v>
+      </x:c>
+      <x:c r="B104" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>赤霞杉苑</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>res://assets/items/icons_simple/23003.png</x:v>
+      </x:c>
+      <x:c r="E104" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H104" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>赤霞杉苑可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J104"/>
+      <x:c r="K104" t="str">
+        <x:v>1101:672;1201:288;1102:28;1202:12</x:v>
+      </x:c>
+      <x:c r="L104" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>24003</x:v>
+      </x:c>
+      <x:c r="B105" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>赤潮灵潭</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>res://assets/items/icons_simple/24003.png</x:v>
+      </x:c>
+      <x:c r="E105" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H105" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>赤潮灵潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J105"/>
+      <x:c r="K105" t="str">
+        <x:v>1301:672;1401:288;1302:28;1402:12</x:v>
+      </x:c>
+      <x:c r="L105" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>25003</x:v>
+      </x:c>
+      <x:c r="B106" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>赤霞矿脉</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>res://assets/items/icons_simple/25003.png</x:v>
+      </x:c>
+      <x:c r="E106" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H106" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>赤霞矿脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J106"/>
+      <x:c r="K106" t="str">
+        <x:v>1501:9120;1502:380;1601:500</x:v>
+      </x:c>
+      <x:c r="L106" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>23004</x:v>
+      </x:c>
+      <x:c r="B107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>月桂灵园</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>res://assets/items/icons_simple/23004.png</x:v>
+      </x:c>
+      <x:c r="E107" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H107" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>月桂灵园可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J107"/>
+      <x:c r="K107" t="str">
+        <x:v>1101:658;1201:282;1102:42;1202:18</x:v>
+      </x:c>
+      <x:c r="L107" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>24004</x:v>
+      </x:c>
+      <x:c r="B108" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>月华鱼湾</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>res://assets/items/icons_simple/24004.png</x:v>
+      </x:c>
+      <x:c r="E108" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H108" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>月华鱼湾可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J108"/>
+      <x:c r="K108" t="str">
+        <x:v>1301:658;1401:282;1302:42;1402:18</x:v>
+      </x:c>
+      <x:c r="L108" t="str"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="n">
+        <x:v>25004</x:v>
+      </x:c>
+      <x:c r="B109" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>月华玉矿</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>res://assets/items/icons_simple/25004.png</x:v>
+      </x:c>
+      <x:c r="E109" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H109" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>月华玉矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J109"/>
+      <x:c r="K109" t="str">
+        <x:v>1501:8930;1502:570;1601:500</x:v>
+      </x:c>
+      <x:c r="L109" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="n">
+        <x:v>23005</x:v>
+      </x:c>
+      <x:c r="B110" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>雷桃仙圃</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>res://assets/items/icons_simple/23005.png</x:v>
+      </x:c>
+      <x:c r="E110" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F110" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H110" t="n">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>雷桃仙圃可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J110"/>
+      <x:c r="K110" t="str">
+        <x:v>1101:644;1201:276;1102:56;1202:24</x:v>
+      </x:c>
+      <x:c r="L110" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="n">
+        <x:v>24005</x:v>
+      </x:c>
+      <x:c r="B111" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>雷鸣灵泽</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>res://assets/items/icons_simple/24005.png</x:v>
+      </x:c>
+      <x:c r="E111" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F111" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H111" t="n">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>雷鸣灵泽可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J111"/>
+      <x:c r="K111" t="str">
+        <x:v>1301:644;1401:276;1302:56;1402:24</x:v>
+      </x:c>
+      <x:c r="L111" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="n">
+        <x:v>25005</x:v>
+      </x:c>
+      <x:c r="B112" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>雷纹矿脉</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>res://assets/items/icons_simple/25005.png</x:v>
+      </x:c>
+      <x:c r="E112" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F112" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H112" t="n">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>雷纹矿脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J112"/>
+      <x:c r="K112" t="str">
+        <x:v>1501:8740;1502:760;1601:500</x:v>
+      </x:c>
+      <x:c r="L112" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>23006</x:v>
+      </x:c>
+      <x:c r="B113" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>冰梧寒苑</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>res://assets/items/icons_simple/23006.png</x:v>
+      </x:c>
+      <x:c r="E113" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H113" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>冰梧寒苑可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J113"/>
+      <x:c r="K113" t="str">
+        <x:v>1101:637;1201:273;1102:63;1202:27</x:v>
+      </x:c>
+      <x:c r="L113" t="str"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>24006</x:v>
+      </x:c>
+      <x:c r="B114" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>玄冰鱼渊</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>res://assets/items/icons_simple/24006.png</x:v>
+      </x:c>
+      <x:c r="E114" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F114" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H114" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>玄冰鱼渊可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J114"/>
+      <x:c r="K114" t="str">
+        <x:v>1301:637;1401:273;1302:63;1402:27</x:v>
+      </x:c>
+      <x:c r="L114" t="str"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>25006</x:v>
+      </x:c>
+      <x:c r="B115" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>玄冰玉脉</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>res://assets/items/icons_simple/25006.png</x:v>
+      </x:c>
+      <x:c r="E115" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H115" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>玄冰玉脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J115"/>
+      <x:c r="K115" t="str">
+        <x:v>1501:8645;1502:855;1601:500</x:v>
+      </x:c>
+      <x:c r="L115" t="str"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>23007</x:v>
+      </x:c>
+      <x:c r="B116" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>地脉沉香园</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>res://assets/items/icons_simple/23007.png</x:v>
+      </x:c>
+      <x:c r="E116" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F116" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H116" t="n">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>地脉沉香园可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J116"/>
+      <x:c r="K116" t="str">
+        <x:v>1101:630;1201:270;1102:70;1202:30</x:v>
+      </x:c>
+      <x:c r="L116" t="str"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>24007</x:v>
+      </x:c>
+      <x:c r="B117" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>地泉灵潭</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>res://assets/items/icons_simple/24007.png</x:v>
+      </x:c>
+      <x:c r="E117" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F117" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H117" t="n">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>地泉灵潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J117"/>
+      <x:c r="K117" t="str">
+        <x:v>1301:630;1401:270;1302:70;1402:30</x:v>
+      </x:c>
+      <x:c r="L117" t="str"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>25007</x:v>
+      </x:c>
+      <x:c r="B118" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>地髓矿脉</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>res://assets/items/icons_simple/25007.png</x:v>
+      </x:c>
+      <x:c r="E118" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G118" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H118" t="n">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>地髓矿脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J118"/>
+      <x:c r="K118" t="str">
+        <x:v>1501:8550;1502:950;1601:500</x:v>
+      </x:c>
+      <x:c r="L118" t="str"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>23008</x:v>
+      </x:c>
+      <x:c r="B119" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>星辉紫檀林</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>res://assets/items/icons_simple/23008.png</x:v>
+      </x:c>
+      <x:c r="E119" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F119" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G119" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H119" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>星辉紫檀林可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J119"/>
+      <x:c r="K119" t="str">
+        <x:v>1101:602;1201:258;1102:84;1202:36;1103:14;1203:6</x:v>
+      </x:c>
+      <x:c r="L119" t="str"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>24008</x:v>
+      </x:c>
+      <x:c r="B120" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>星澜鱼海</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>res://assets/items/icons_simple/24008.png</x:v>
+      </x:c>
+      <x:c r="E120" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F120" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G120" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H120" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>星澜鱼海可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J120"/>
+      <x:c r="K120" t="str">
+        <x:v>1301:602;1401:258;1302:84;1402:36;1303:14;1403:6</x:v>
+      </x:c>
+      <x:c r="L120" t="str"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>25008</x:v>
+      </x:c>
+      <x:c r="B121" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>星辉玉矿</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>res://assets/items/icons_simple/25008.png</x:v>
+      </x:c>
+      <x:c r="E121" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F121" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G121" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H121" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>星辉玉矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J121"/>
+      <x:c r="K121" t="str">
+        <x:v>1501:8170;1502:1140;1503:190;1601:500</x:v>
+      </x:c>
+      <x:c r="L121" t="str"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>23009</x:v>
+      </x:c>
+      <x:c r="B122" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>龙血古木境</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>res://assets/items/icons_simple/23009.png</x:v>
+      </x:c>
+      <x:c r="E122" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G122" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H122" t="n">
+        <x:v>6600</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>龙血古木境可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J122"/>
+      <x:c r="K122" t="str">
+        <x:v>1101:574;1201:246;1102:105;1202:45;1103:21;1203:9</x:v>
+      </x:c>
+      <x:c r="L122" t="str"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>24009</x:v>
+      </x:c>
+      <x:c r="B123" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>龙涎灵池</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>res://assets/items/icons_simple/24009.png</x:v>
+      </x:c>
+      <x:c r="E123" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F123" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G123" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H123" t="n">
+        <x:v>6600</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>龙涎灵池可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J123"/>
+      <x:c r="K123" t="str">
+        <x:v>1301:574;1401:246;1302:105;1402:45;1303:21;1403:9</x:v>
+      </x:c>
+      <x:c r="L123" t="str"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="n">
+        <x:v>25009</x:v>
+      </x:c>
+      <x:c r="B124" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>龙脉矿藏</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>res://assets/items/icons_simple/25009.png</x:v>
+      </x:c>
+      <x:c r="E124" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F124" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H124" t="n">
+        <x:v>6600</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>龙脉矿藏可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J124"/>
+      <x:c r="K124" t="str">
+        <x:v>1501:7790;1502:1425;1503:285;1601:500</x:v>
+      </x:c>
+      <x:c r="L124" t="str"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="n">
+        <x:v>23010</x:v>
+      </x:c>
+      <x:c r="B125" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>凤栖神木园</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>res://assets/items/icons_simple/23010.png</x:v>
+      </x:c>
+      <x:c r="E125" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F125" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G125" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H125" t="n">
+        <x:v>7200</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>凤栖神木园可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J125"/>
+      <x:c r="K125" t="str">
+        <x:v>1101:532;1201:228;1102:140;1202:60;1103:28;1203:12</x:v>
+      </x:c>
+      <x:c r="L125" t="str"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="n">
+        <x:v>24010</x:v>
+      </x:c>
+      <x:c r="B126" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>凤影锦潭</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>res://assets/items/icons_simple/24010.png</x:v>
+      </x:c>
+      <x:c r="E126" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F126" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H126" t="n">
+        <x:v>7200</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>凤影锦潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J126"/>
+      <x:c r="K126" t="str">
+        <x:v>1301:532;1401:228;1302:140;1402:60;1303:28;1403:12</x:v>
+      </x:c>
+      <x:c r="L126" t="str"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="n">
+        <x:v>25010</x:v>
+      </x:c>
+      <x:c r="B127" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>凤华玉脉</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>res://assets/items/icons_simple/25010.png</x:v>
+      </x:c>
+      <x:c r="E127" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F127" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G127" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H127" t="n">
+        <x:v>7200</x:v>
+      </x:c>
+      <x:c r="I127" t="str">
+        <x:v>凤华玉脉可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J127"/>
+      <x:c r="K127" t="str">
+        <x:v>1501:7220;1502:1900;1503:380;1601:500</x:v>
+      </x:c>
+      <x:c r="L127" t="str"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="n">
+        <x:v>23011</x:v>
+      </x:c>
+      <x:c r="B128" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>九幽玄木界</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>res://assets/items/icons_simple/23011.png</x:v>
+      </x:c>
+      <x:c r="E128" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F128" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G128" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H128" t="n">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="I128" t="str">
+        <x:v>九幽玄木界可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J128"/>
+      <x:c r="K128" t="str">
+        <x:v>1101:490;1201:210;1102:175;1202:75;1103:35;1203:15</x:v>
+      </x:c>
+      <x:c r="L128" t="str"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="n">
+        <x:v>24011</x:v>
+      </x:c>
+      <x:c r="B129" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>九幽玄渊</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>res://assets/items/icons_simple/24011.png</x:v>
+      </x:c>
+      <x:c r="E129" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F129" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G129" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H129" t="n">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="I129" t="str">
+        <x:v>九幽玄渊可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J129"/>
+      <x:c r="K129" t="str">
+        <x:v>1301:490;1401:210;1302:175;1402:75;1303:35;1403:15</x:v>
+      </x:c>
+      <x:c r="L129" t="str"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="n">
+        <x:v>25011</x:v>
+      </x:c>
+      <x:c r="B130" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>九幽玄矿</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>res://assets/items/icons_simple/25011.png</x:v>
+      </x:c>
+      <x:c r="E130" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F130" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G130" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H130" t="n">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="I130" t="str">
+        <x:v>九幽玄矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J130"/>
+      <x:c r="K130" t="str">
+        <x:v>1501:6650;1502:2375;1503:475;1601:500</x:v>
+      </x:c>
+      <x:c r="L130" t="str"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="n">
+        <x:v>23012</x:v>
+      </x:c>
+      <x:c r="B131" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>扶桑日轮苑</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>res://assets/items/icons_simple/23012.png</x:v>
+      </x:c>
+      <x:c r="E131" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G131" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H131" t="n">
+        <x:v>8400</x:v>
+      </x:c>
+      <x:c r="I131" t="str">
+        <x:v>扶桑日轮苑可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J131"/>
+      <x:c r="K131" t="str">
+        <x:v>1101:462;1201:198;1102:182;1202:78;1103:49;1203:21;1104:7;1204:3</x:v>
+      </x:c>
+      <x:c r="L131" t="str"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="n">
+        <x:v>24012</x:v>
+      </x:c>
+      <x:c r="B132" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>扶桑日潭</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>res://assets/items/icons_simple/24012.png</x:v>
+      </x:c>
+      <x:c r="E132" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F132" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G132" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H132" t="n">
+        <x:v>8400</x:v>
+      </x:c>
+      <x:c r="I132" t="str">
+        <x:v>扶桑日潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J132"/>
+      <x:c r="K132" t="str">
+        <x:v>1301:462;1401:198;1302:182;1402:78;1303:49;1403:21;1304:7;1404:3</x:v>
+      </x:c>
+      <x:c r="L132" t="str"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="n">
+        <x:v>25012</x:v>
+      </x:c>
+      <x:c r="B133" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>扶桑阳矿</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>res://assets/items/icons_simple/25012.png</x:v>
+      </x:c>
+      <x:c r="E133" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F133" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G133" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H133" t="n">
+        <x:v>8400</x:v>
+      </x:c>
+      <x:c r="I133" t="str">
+        <x:v>扶桑阳矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J133"/>
+      <x:c r="K133" t="str">
+        <x:v>1501:6270;1502:2470;1503:665;1504:95;1601:500</x:v>
+      </x:c>
+      <x:c r="L133" t="str"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="n">
+        <x:v>23013</x:v>
+      </x:c>
+      <x:c r="B134" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>建木灵境</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>res://assets/items/icons_simple/23013.png</x:v>
+      </x:c>
+      <x:c r="E134" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G134" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H134" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>建木灵境可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J134"/>
+      <x:c r="K134" t="str">
+        <x:v>1101:434;1201:186;1102:189;1202:81;1103:63;1203:27;1104:14;1204:6</x:v>
+      </x:c>
+      <x:c r="L134" t="str"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="n">
+        <x:v>24013</x:v>
+      </x:c>
+      <x:c r="B135" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>建木碧泽</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>res://assets/items/icons_simple/24013.png</x:v>
+      </x:c>
+      <x:c r="E135" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G135" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H135" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>建木碧泽可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J135"/>
+      <x:c r="K135" t="str">
+        <x:v>1301:434;1401:186;1302:189;1402:81;1303:63;1403:27;1304:14;1404:6</x:v>
+      </x:c>
+      <x:c r="L135" t="str"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="n">
+        <x:v>25013</x:v>
+      </x:c>
+      <x:c r="B136" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>建木碧矿</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>res://assets/items/icons_simple/25013.png</x:v>
+      </x:c>
+      <x:c r="E136" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F136" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G136" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H136" t="n">
+        <x:v>9000</x:v>
+      </x:c>
+      <x:c r="I136" t="str">
+        <x:v>建木碧矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J136"/>
+      <x:c r="K136" t="str">
+        <x:v>1501:5890;1502:2565;1503:855;1504:190;1601:500</x:v>
+      </x:c>
+      <x:c r="L136" t="str"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="n">
+        <x:v>23014</x:v>
+      </x:c>
+      <x:c r="B137" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>菩提道园</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>res://assets/items/icons_simple/23014.png</x:v>
+      </x:c>
+      <x:c r="E137" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G137" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H137" t="n">
+        <x:v>9600</x:v>
+      </x:c>
+      <x:c r="I137" t="str">
+        <x:v>菩提道园可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J137"/>
+      <x:c r="K137" t="str">
+        <x:v>1101:406;1201:174;1102:196;1202:84;1103:77;1203:33;1104:21;1204:9</x:v>
+      </x:c>
+      <x:c r="L137" t="str"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="n">
+        <x:v>24014</x:v>
+      </x:c>
+      <x:c r="B138" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>菩提慧海</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>res://assets/items/icons_simple/24014.png</x:v>
+      </x:c>
+      <x:c r="E138" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F138" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G138" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H138" t="n">
+        <x:v>9600</x:v>
+      </x:c>
+      <x:c r="I138" t="str">
+        <x:v>菩提慧海可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J138"/>
+      <x:c r="K138" t="str">
+        <x:v>1301:406;1401:174;1302:196;1402:84;1303:77;1403:33;1304:21;1404:9</x:v>
+      </x:c>
+      <x:c r="L138" t="str"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="n">
+        <x:v>25014</x:v>
+      </x:c>
+      <x:c r="B139" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>菩提心矿</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>res://assets/items/icons_simple/25014.png</x:v>
+      </x:c>
+      <x:c r="E139" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G139" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H139" t="n">
+        <x:v>9600</x:v>
+      </x:c>
+      <x:c r="I139" t="str">
+        <x:v>菩提心矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J139"/>
+      <x:c r="K139" t="str">
+        <x:v>1501:5510;1502:2660;1503:1045;1504:285;1601:500</x:v>
+      </x:c>
+      <x:c r="L139" t="str"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="n">
+        <x:v>23015</x:v>
+      </x:c>
+      <x:c r="B140" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>鸿蒙祖木界</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>res://assets/items/icons_simple/23015.png</x:v>
+      </x:c>
+      <x:c r="E140" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G140" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H140" t="n">
+        <x:v>10200</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>鸿蒙祖木界可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J140"/>
+      <x:c r="K140" t="str">
+        <x:v>1101:378;1201:162;1102:203;1202:87;1103:91;1203:39;1104:28;1204:12</x:v>
+      </x:c>
+      <x:c r="L140" t="str"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="n">
+        <x:v>24015</x:v>
+      </x:c>
+      <x:c r="B141" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>鸿蒙灵洋</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>res://assets/items/icons_simple/24015.png</x:v>
+      </x:c>
+      <x:c r="E141" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G141" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H141" t="n">
+        <x:v>10200</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>鸿蒙灵洋可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J141"/>
+      <x:c r="K141" t="str">
+        <x:v>1301:378;1401:162;1302:203;1402:87;1303:91;1403:39;1304:28;1404:12</x:v>
+      </x:c>
+      <x:c r="L141" t="str"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="n">
+        <x:v>25015</x:v>
+      </x:c>
+      <x:c r="B142" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>鸿蒙源矿</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>res://assets/items/icons_simple/25015.png</x:v>
+      </x:c>
+      <x:c r="E142" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F142" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G142" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H142" t="n">
+        <x:v>10200</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>鸿蒙源矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J142"/>
+      <x:c r="K142" t="str">
+        <x:v>1501:5130;1502:2755;1503:1235;1504:380;1601:500</x:v>
+      </x:c>
+      <x:c r="L142" t="str"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="n">
+        <x:v>23016</x:v>
+      </x:c>
+      <x:c r="B143" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>太初世界林</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>res://assets/items/icons_simple/23016.png</x:v>
+      </x:c>
+      <x:c r="E143" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G143" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H143" t="n">
+        <x:v>10800</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>太初世界林可培育灵木并伴生灵脂。</x:v>
+      </x:c>
+      <x:c r="J143"/>
+      <x:c r="K143" t="str">
+        <x:v>1101:350;1201:150;1102:210;1202:90;1103:105;1203:45;1104:35;1204:15</x:v>
+      </x:c>
+      <x:c r="L143" t="str"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="n">
+        <x:v>24016</x:v>
+      </x:c>
+      <x:c r="B144" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>太初神潭</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>res://assets/items/icons_simple/24016.png</x:v>
+      </x:c>
+      <x:c r="E144" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F144" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H144" t="n">
+        <x:v>10800</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>太初神潭可孕养灵鱼并凝结灵珠。</x:v>
+      </x:c>
+      <x:c r="J144"/>
+      <x:c r="K144" t="str">
+        <x:v>1301:350;1401:150;1302:210;1402:90;1303:105;1403:45;1304:35;1404:15</x:v>
+      </x:c>
+      <x:c r="L144" t="str"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="n">
+        <x:v>25016</x:v>
+      </x:c>
+      <x:c r="B145" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>太初神矿</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>res://assets/items/icons_simple/25016.png</x:v>
+      </x:c>
+      <x:c r="E145" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F145" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H145" t="n">
+        <x:v>10800</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>太初神矿可开采玉石并偶尔产出可使用的灵石。</x:v>
+      </x:c>
+      <x:c r="J145"/>
+      <x:c r="K145" t="str">
+        <x:v>1501:4750;1502:2850;1503:1425;1504:475;1601:500</x:v>
+      </x:c>
+      <x:c r="L145" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -24038,10 +29293,8 @@
       <x:c r="B2" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">陶纹药炉</x:t>
-        </x:is>
+      <x:c r="C2" s="3" t="str">
+        <x:v>陶纹药炉</x:v>
       </x:c>
       <x:c r="D2" s="3" t="n">
         <x:v>31</x:v>
@@ -24049,20 +29302,14 @@
       <x:c r="E2" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17001.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">陶纹药炉以陶土与松炭筑成，炉腹留有旧火温度。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F2" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17001.png</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="str">
+        <x:v>陶纹药炉以陶土与松炭筑成，炉腹留有旧火温度。</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -24072,10 +29319,8 @@
       <x:c r="B3" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青砖丹灶</x:t>
-        </x:is>
+      <x:c r="C3" s="3" t="str">
+        <x:v>青砖丹灶</x:v>
       </x:c>
       <x:c r="D3" s="3" t="n">
         <x:v>31</x:v>
@@ -24083,20 +29328,14 @@
       <x:c r="E3" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17002.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青砖丹灶立于溪谷缓坡，灶门上青烟盘旋不散。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F3" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17002.png</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>青砖丹灶立于溪谷缓坡，灶门上青烟盘旋不散。</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -24106,10 +29345,8 @@
       <x:c r="B4" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤铜云炉</x:t>
-        </x:is>
+      <x:c r="C4" s="3" t="str">
+        <x:v>赤铜云炉</x:v>
       </x:c>
       <x:c r="D4" s="3" t="n">
         <x:v>31</x:v>
@@ -24117,20 +29354,14 @@
       <x:c r="E4" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17003.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取赤铜与云母建成赤铜云炉，铜壁映出流云般的暗纹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F4" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17003.png</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="str">
+        <x:v>匠人取赤铜与云母建成赤铜云炉，铜壁映出流云般的暗纹。</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -24140,10 +29371,8 @@
       <x:c r="B5" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄铁丹鼎</x:t>
-        </x:is>
+      <x:c r="C5" s="3" t="str">
+        <x:v>玄铁丹鼎</x:v>
       </x:c>
       <x:c r="D5" s="3" t="n">
         <x:v>31</x:v>
@@ -24151,20 +29380,14 @@
       <x:c r="E5" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17004.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻玄铁丹鼎旧址在云崖石台，鼎耳沉重如伏兽。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F5" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17004.png</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="str">
+        <x:v>传闻玄铁丹鼎旧址在云崖石台，鼎耳沉重如伏兽。</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -24174,10 +29397,8 @@
       <x:c r="B6" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒玉冰釜</x:t>
-        </x:is>
+      <x:c r="C6" s="3" t="str">
+        <x:v>寒玉冰釜</x:v>
       </x:c>
       <x:c r="D6" s="3" t="n">
         <x:v>31</x:v>
@@ -24185,20 +29406,14 @@
       <x:c r="E6" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17005.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒谷背阴处所见的寒玉冰釜由寒玉与冰晶构成，釜沿终年凝着白霜。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F6" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17005.png</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="str">
+        <x:v>寒谷背阴处所见的寒玉冰釜由寒玉与冰晶构成，釜沿终年凝着白霜。</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -24208,10 +29423,8 @@
       <x:c r="B7" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火丹炉</x:t>
-        </x:is>
+      <x:c r="C7" s="3" t="str">
+        <x:v>离火丹炉</x:v>
       </x:c>
       <x:c r="D7" s="3" t="n">
         <x:v>31</x:v>
@@ -24219,20 +29432,14 @@
       <x:c r="E7" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17006.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火丹炉以离火石与赤铜筑成，炉火熄灭后仍有赤光。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F7" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17006.png</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="str">
+        <x:v>离火丹炉以离火石与赤铜筑成，炉火熄灭后仍有赤光。</x:v>
+      </x:c>
+      <x:c r="H7" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -24242,10 +29449,8 @@
       <x:c r="B8" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">苍梧木鼎</x:t>
-        </x:is>
+      <x:c r="C8" s="3" t="str">
+        <x:v>苍梧木鼎</x:v>
       </x:c>
       <x:c r="D8" s="3" t="n">
         <x:v>31</x:v>
@@ -24253,20 +29458,14 @@
       <x:c r="E8" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17007.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">苍梧木鼎立于苍梧秘境，木鼎近火而不见焦痕。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F8" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17007.png</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="str">
+        <x:v>苍梧木鼎立于苍梧秘境，木鼎近火而不见焦痕。</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -24276,10 +29475,8 @@
       <x:c r="B9" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九霄雷炉</x:t>
-        </x:is>
+      <x:c r="C9" s="3" t="str">
+        <x:v>九霄雷炉</x:v>
       </x:c>
       <x:c r="D9" s="3" t="n">
         <x:v>31</x:v>
@@ -24287,20 +29484,14 @@
       <x:c r="E9" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17008.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取雷纹铜与黑石建成九霄雷炉，雷雨时炉身自鸣。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F9" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17008.png</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="str">
+        <x:v>匠人取雷纹铜与黑石建成九霄雷炉，雷雨时炉身自鸣。</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -24310,10 +29501,8 @@
       <x:c r="B10" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">坤元地鼎</x:t>
-        </x:is>
+      <x:c r="C10" s="3" t="str">
+        <x:v>坤元地鼎</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
         <x:v>31</x:v>
@@ -24321,20 +29510,14 @@
       <x:c r="E10" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17009.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻坤元地鼎旧址在坤元地脉，地脉气息沿炉壁缓缓升起。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F10" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17009.png</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="str">
+        <x:v>传闻坤元地鼎旧址在坤元地脉，地脉气息沿炉壁缓缓升起。</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -24344,10 +29527,8 @@
       <x:c r="B11" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星陨丹台</x:t>
-        </x:is>
+      <x:c r="C11" s="3" t="str">
+        <x:v>星陨丹台</x:v>
       </x:c>
       <x:c r="D11" s="3" t="n">
         <x:v>31</x:v>
@@ -24355,20 +29536,14 @@
       <x:c r="E11" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17010.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星落天原所见的星陨丹台由星陨铁与天河砂构成，夜间炉壁会映出群星轨迹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F11" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17010.png</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>星落天原所见的星陨丹台由星陨铁与天河砂构成，夜间炉壁会映出群星轨迹。</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -24378,10 +29553,8 @@
       <x:c r="B12" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟云炉</x:t>
-        </x:is>
+      <x:c r="C12" s="3" t="str">
+        <x:v>紫烟云炉</x:v>
       </x:c>
       <x:c r="D12" s="3" t="n">
         <x:v>31</x:v>
@@ -24389,20 +29562,14 @@
       <x:c r="E12" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17011.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟云炉以紫府玉与烟霞木筑成，紫色云烟常在炉壁周围盘旋。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F12" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17011.png</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>紫烟云炉以紫府玉与烟霞木筑成，紫色云烟常在炉壁周围盘旋。</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -24412,10 +29579,8 @@
       <x:c r="B13" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C13" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍丹宫</x:t>
-        </x:is>
+      <x:c r="C13" s="3" t="str">
+        <x:v>九窍丹宫</x:v>
       </x:c>
       <x:c r="D13" s="3" t="n">
         <x:v>31</x:v>
@@ -24423,20 +29588,14 @@
       <x:c r="E13" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17012.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍丹宫立于九曲地宫，炉壁依九曲方位层层展开。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F13" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17012.png</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>九窍丹宫立于九曲地宫，炉壁依九曲方位层层展开。</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -24446,10 +29605,8 @@
       <x:c r="B14" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅火神炉</x:t>
-        </x:is>
+      <x:c r="C14" s="3" t="str">
+        <x:v>涅火神炉</x:v>
       </x:c>
       <x:c r="D14" s="3" t="n">
         <x:v>31</x:v>
@@ -24457,20 +29614,14 @@
       <x:c r="E14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17013.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取涅火晶与赤金建成涅火神炉，赤金纹路随天火明灭不定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F14" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17013.png</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>匠人取涅火晶与赤金建成涅火神炉，赤金纹路随天火明灭不定。</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -24480,10 +29631,8 @@
       <x:c r="B15" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙纹天鼎</x:t>
-        </x:is>
+      <x:c r="C15" s="3" t="str">
+        <x:v>龙纹天鼎</x:v>
       </x:c>
       <x:c r="D15" s="3" t="n">
         <x:v>31</x:v>
@@ -24491,20 +29640,14 @@
       <x:c r="E15" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17014.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻龙纹天鼎旧址在龙眠古渊，炉壁上隐约盘着龙形云气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F15" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17014.png</x:v>
+      </x:c>
+      <x:c r="G15" s="3" t="str">
+        <x:v>传闻龙纹天鼎旧址在龙眠古渊，炉壁上隐约盘着龙形云气。</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -24514,10 +29657,8 @@
       <x:c r="B16" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖丹窑</x:t>
-        </x:is>
+      <x:c r="C16" s="3" t="str">
+        <x:v>凤栖丹窑</x:v>
       </x:c>
       <x:c r="D16" s="3" t="n">
         <x:v>31</x:v>
@@ -24525,20 +29666,14 @@
       <x:c r="E16" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17015.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖神木所见的凤栖丹窑由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F16" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17015.png</x:v>
+      </x:c>
+      <x:c r="G16" s="3" t="str">
+        <x:v>凤栖神木所见的凤栖丹窑由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -24548,10 +29683,8 @@
       <x:c r="B17" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C17" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初造化炉</x:t>
-        </x:is>
+      <x:c r="C17" s="3" t="str">
+        <x:v>太初造化炉</x:v>
       </x:c>
       <x:c r="D17" s="3" t="n">
         <x:v>31</x:v>
@@ -24559,20 +29692,14 @@
       <x:c r="E17" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/17016.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初造化炉以太初晶与鸿蒙母金筑成，近看炉壁仿佛隔着太初雾海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210</x:t>
-        </x:is>
+      <x:c r="F17" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/17016.png</x:v>
+      </x:c>
+      <x:c r="G17" s="3" t="str">
+        <x:v>太初造化炉以太初晶与鸿蒙母金筑成，近看炉壁仿佛隔着太初雾海。</x:v>
+      </x:c>
+      <x:c r="H17" s="3" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;99;100;199;200;201;202;203;204;205;206;207;208;209;210;211;212;213;214;215;216;217;218;219;220</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -24582,10 +29709,8 @@
       <x:c r="B18" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C18" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">石砧铁锤</x:t>
-        </x:is>
+      <x:c r="C18" s="3" t="str">
+        <x:v>石砧铁锤</x:v>
       </x:c>
       <x:c r="D18" s="3" t="n">
         <x:v>32</x:v>
@@ -24593,20 +29718,14 @@
       <x:c r="E18" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18001.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">石砧铁锤以山石与乌铁筑成，砧面布满细密锤痕。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F18" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18001.png</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="str">
+        <x:v>石砧铁锤以山石与乌铁筑成，砧面布满细密锤痕。</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -24616,10 +29735,8 @@
       <x:c r="B19" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C19" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松炭锻炉</x:t>
-        </x:is>
+      <x:c r="C19" s="3" t="str">
+        <x:v>松炭锻炉</x:v>
       </x:c>
       <x:c r="D19" s="3" t="n">
         <x:v>32</x:v>
@@ -24627,20 +29744,14 @@
       <x:c r="E19" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F19" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18002.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松炭锻炉立于溪谷缓坡，炉膛带着松脂焦香。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F19" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18002.png</x:v>
+      </x:c>
+      <x:c r="G19" s="3" t="str">
+        <x:v>松炭锻炉立于溪谷缓坡，炉膛带着松脂焦香。</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -24650,10 +29761,8 @@
       <x:c r="B20" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤铜锻台</x:t>
-        </x:is>
+      <x:c r="C20" s="3" t="str">
+        <x:v>赤铜锻台</x:v>
       </x:c>
       <x:c r="D20" s="3" t="n">
         <x:v>32</x:v>
@@ -24661,20 +29770,14 @@
       <x:c r="E20" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18003.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取赤铜与厚木建成赤铜锻台，台角垂着暗红铜屑。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F20" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18003.png</x:v>
+      </x:c>
+      <x:c r="G20" s="3" t="str">
+        <x:v>匠人取赤铜与厚木建成赤铜锻台，台角垂着暗红铜屑。</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -24684,10 +29787,8 @@
       <x:c r="B21" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C21" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄铁金砧</x:t>
-        </x:is>
+      <x:c r="C21" s="3" t="str">
+        <x:v>玄铁金砧</x:v>
       </x:c>
       <x:c r="D21" s="3" t="n">
         <x:v>32</x:v>
@@ -24695,20 +29796,14 @@
       <x:c r="E21" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F21" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18004.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻玄铁金砧旧址在云崖石台，金砧敲击时声如龙吟。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F21" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18004.png</x:v>
+      </x:c>
+      <x:c r="G21" s="3" t="str">
+        <x:v>传闻玄铁金砧旧址在云崖石台，金砧敲击时声如龙吟。</x:v>
+      </x:c>
+      <x:c r="H21" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -24718,10 +29813,8 @@
       <x:c r="B22" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C22" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒渊淬池</x:t>
-        </x:is>
+      <x:c r="C22" s="3" t="str">
+        <x:v>寒渊淬池</x:v>
       </x:c>
       <x:c r="D22" s="3" t="n">
         <x:v>32</x:v>
@@ -24729,20 +29822,14 @@
       <x:c r="E22" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18005.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G22" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒谷背阴处所见的寒渊淬池由寒铁与冰岩构成，池水上常浮寒白雾气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F22" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18005.png</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="str">
+        <x:v>寒谷背阴处所见的寒渊淬池由寒铁与冰岩构成，池水上常浮寒白雾气。</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -24752,10 +29839,8 @@
       <x:c r="B23" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C23" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地火熔炉</x:t>
-        </x:is>
+      <x:c r="C23" s="3" t="str">
+        <x:v>地火熔炉</x:v>
       </x:c>
       <x:c r="D23" s="3" t="n">
         <x:v>32</x:v>
@@ -24763,20 +29848,14 @@
       <x:c r="E23" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F23" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18006.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G23" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地火熔炉以地火石与炎晶筑成，熔炉深处似有地火呼吸。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F23" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18006.png</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="str">
+        <x:v>地火熔炉以地火石与炎晶筑成，熔炉深处似有地火呼吸。</x:v>
+      </x:c>
+      <x:c r="H23" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -24786,10 +29865,8 @@
       <x:c r="B24" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C24" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青罡玉砧</x:t>
-        </x:is>
+      <x:c r="C24" s="3" t="str">
+        <x:v>青罡玉砧</x:v>
       </x:c>
       <x:c r="D24" s="3" t="n">
         <x:v>32</x:v>
@@ -24797,20 +29874,14 @@
       <x:c r="E24" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F24" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18007.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青罡玉砧立于苍梧秘境，玉砧表面毫无裂纹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F24" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18007.png</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="str">
+        <x:v>青罡玉砧立于苍梧秘境，玉砧表面毫无裂纹。</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -24820,10 +29891,8 @@
       <x:c r="B25" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C25" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷火锻台</x:t>
-        </x:is>
+      <x:c r="C25" s="3" t="str">
+        <x:v>雷火锻台</x:v>
       </x:c>
       <x:c r="D25" s="3" t="n">
         <x:v>32</x:v>
@@ -24831,20 +29900,14 @@
       <x:c r="E25" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F25" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18008.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G25" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取雷砂与玄铁建成雷火锻台，锻台边缘常有电芒跳跃。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F25" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18008.png</x:v>
+      </x:c>
+      <x:c r="G25" s="3" t="str">
+        <x:v>匠人取雷砂与玄铁建成雷火锻台，锻台边缘常有电芒跳跃。</x:v>
+      </x:c>
+      <x:c r="H25" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -24854,10 +29917,8 @@
       <x:c r="B26" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C26" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">坤岳重炉</x:t>
-        </x:is>
+      <x:c r="C26" s="3" t="str">
+        <x:v>坤岳重炉</x:v>
       </x:c>
       <x:c r="D26" s="3" t="n">
         <x:v>32</x:v>
@@ -24865,20 +29926,14 @@
       <x:c r="E26" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F26" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18009.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G26" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻坤岳重炉旧址在坤元地脉，地脉气息沿砧台缓缓升起。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F26" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18009.png</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="str">
+        <x:v>传闻坤岳重炉旧址在坤元地脉，地脉气息沿砧台缓缓升起。</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -24888,10 +29943,8 @@
       <x:c r="B27" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C27" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星陨熔坊</x:t>
-        </x:is>
+      <x:c r="C27" s="3" t="str">
+        <x:v>星陨熔坊</x:v>
       </x:c>
       <x:c r="D27" s="3" t="n">
         <x:v>32</x:v>
@@ -24899,20 +29952,14 @@
       <x:c r="E27" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18010.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G27" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星落天原所见的星陨熔坊由星陨铁与天河砂构成，夜间砧台会映出群星轨迹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H27" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F27" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18010.png</x:v>
+      </x:c>
+      <x:c r="G27" s="3" t="str">
+        <x:v>星落天原所见的星陨熔坊由星陨铁与天河砂构成，夜间砧台会映出群星轨迹。</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -24922,10 +29969,8 @@
       <x:c r="B28" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C28" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太虚锻宫</x:t>
-        </x:is>
+      <x:c r="C28" s="3" t="str">
+        <x:v>太虚锻宫</x:v>
       </x:c>
       <x:c r="D28" s="3" t="n">
         <x:v>32</x:v>
@@ -24933,20 +29978,14 @@
       <x:c r="E28" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F28" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18011.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太虚锻宫以紫府玉与烟霞木筑成，紫色云烟常在砧台周围盘旋。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F28" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18011.png</x:v>
+      </x:c>
+      <x:c r="G28" s="3" t="str">
+        <x:v>太虚锻宫以紫府玉与烟霞木筑成，紫色云烟常在砧台周围盘旋。</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -24956,10 +29995,8 @@
       <x:c r="B29" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C29" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九幽铸台</x:t>
-        </x:is>
+      <x:c r="C29" s="3" t="str">
+        <x:v>九幽铸台</x:v>
       </x:c>
       <x:c r="D29" s="3" t="n">
         <x:v>32</x:v>
@@ -24967,20 +30004,14 @@
       <x:c r="E29" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F29" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18012.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G29" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九幽铸台立于九曲地宫，砧台依九曲方位层层展开。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F29" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18012.png</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="str">
+        <x:v>九幽铸台立于九曲地宫，砧台依九曲方位层层展开。</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -24990,10 +30021,8 @@
       <x:c r="B30" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C30" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">日精金炉</x:t>
-        </x:is>
+      <x:c r="C30" s="3" t="str">
+        <x:v>日精金炉</x:v>
       </x:c>
       <x:c r="D30" s="3" t="n">
         <x:v>32</x:v>
@@ -25001,20 +30030,14 @@
       <x:c r="E30" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18013.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取涅火晶与赤金建成日精金炉，赤金纹路随天火明灭不定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F30" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18013.png</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="str">
+        <x:v>匠人取涅火晶与赤金建成日精金炉，赤金纹路随天火明灭不定。</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -25024,10 +30047,8 @@
       <x:c r="B31" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C31" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月魄寒坊</x:t>
-        </x:is>
+      <x:c r="C31" s="3" t="str">
+        <x:v>月魄寒坊</x:v>
       </x:c>
       <x:c r="D31" s="3" t="n">
         <x:v>32</x:v>
@@ -25035,20 +30056,14 @@
       <x:c r="E31" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F31" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18014.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G31" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻月魄寒坊旧址在龙眠古渊，砧台上隐约盘着龙形云气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F31" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18014.png</x:v>
+      </x:c>
+      <x:c r="G31" s="3" t="str">
+        <x:v>传闻月魄寒坊旧址在龙眠古渊，砧台上隐约盘着龙形云气。</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -25058,10 +30073,8 @@
       <x:c r="B32" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C32" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">天河铸宫</x:t>
-        </x:is>
+      <x:c r="C32" s="3" t="str">
+        <x:v>天河铸宫</x:v>
       </x:c>
       <x:c r="D32" s="3" t="n">
         <x:v>32</x:v>
@@ -25069,20 +30082,14 @@
       <x:c r="E32" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F32" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18015.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G32" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖神木所见的天河铸宫由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F32" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18015.png</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="str">
+        <x:v>凤栖神木所见的天河铸宫由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -25092,10 +30099,8 @@
       <x:c r="B33" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C33" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鸿蒙炼天鼎</x:t>
-        </x:is>
+      <x:c r="C33" s="3" t="str">
+        <x:v>鸿蒙炼天鼎</x:v>
       </x:c>
       <x:c r="D33" s="3" t="n">
         <x:v>32</x:v>
@@ -25103,20 +30108,14 @@
       <x:c r="E33" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/18016.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G33" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鸿蒙炼天鼎以太初晶与鸿蒙母金筑成，近看砧台仿佛隔着太初雾海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166</x:t>
-        </x:is>
+      <x:c r="F33" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/18016.png</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="str">
+        <x:v>鸿蒙炼天鼎以太初晶与鸿蒙母金筑成，近看砧台仿佛隔着太初雾海。</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="str">
+        <x:v>151;152;153;154;155;156;157;158;159;160;161;162;163;164;165;166;231;232;233;234;235;236;237;238;239;240</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -25126,10 +30125,8 @@
       <x:c r="B34" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C34" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">竹席演阵台</x:t>
-        </x:is>
+      <x:c r="C34" s="3" t="str">
+        <x:v>竹席演阵台</x:v>
       </x:c>
       <x:c r="D34" s="3" t="n">
         <x:v>33</x:v>
@@ -25137,20 +30134,14 @@
       <x:c r="E34" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F34" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19001.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G34" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">竹席演阵台以竹席与河石筑成，席上经纬线宛如山川。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F34" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19001.png</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="str">
+        <x:v>竹席演阵台以竹席与河石筑成，席上经纬线宛如山川。</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -25160,10 +30151,8 @@
       <x:c r="B35" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松盘布阵桌</x:t>
-        </x:is>
+      <x:c r="C35" s="3" t="str">
+        <x:v>松盘布阵桌</x:v>
       </x:c>
       <x:c r="D35" s="3" t="n">
         <x:v>33</x:v>
@@ -25171,20 +30160,14 @@
       <x:c r="E35" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F35" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19002.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G35" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松盘布阵桌立于溪谷缓坡，木盘刻着细小星位。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F35" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19002.png</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="str">
+        <x:v>松盘布阵桌立于溪谷缓坡，木盘刻着细小星位。</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -25194,10 +30177,8 @@
       <x:c r="B36" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C36" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">铜镜阵台</x:t>
-        </x:is>
+      <x:c r="C36" s="3" t="str">
+        <x:v>铜镜阵台</x:v>
       </x:c>
       <x:c r="D36" s="3" t="n">
         <x:v>33</x:v>
@@ -25205,20 +30186,14 @@
       <x:c r="E36" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F36" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19003.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G36" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取铜镜与青石建成铜镜阵台，铜镜会映出重叠阵纹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F36" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19003.png</x:v>
+      </x:c>
+      <x:c r="G36" s="3" t="str">
+        <x:v>匠人取铜镜与青石建成铜镜阵台，铜镜会映出重叠阵纹。</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -25228,10 +30203,8 @@
       <x:c r="B37" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C37" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄铁棋阵</x:t>
-        </x:is>
+      <x:c r="C37" s="3" t="str">
+        <x:v>玄铁棋阵</x:v>
       </x:c>
       <x:c r="D37" s="3" t="n">
         <x:v>33</x:v>
@@ -25239,20 +30212,14 @@
       <x:c r="E37" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F37" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19004.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G37" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻玄铁棋阵旧址在云崖石台，棋子落下时余音悠长。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F37" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19004.png</x:v>
+      </x:c>
+      <x:c r="G37" s="3" t="str">
+        <x:v>传闻玄铁棋阵旧址在云崖石台，棋子落下时余音悠长。</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -25262,10 +30229,8 @@
       <x:c r="B38" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C38" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰晶阵座</x:t>
-        </x:is>
+      <x:c r="C38" s="3" t="str">
+        <x:v>冰晶阵座</x:v>
       </x:c>
       <x:c r="D38" s="3" t="n">
         <x:v>33</x:v>
@@ -25273,20 +30238,14 @@
       <x:c r="E38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19005.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G38" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒谷背阴处所见的冰晶阵座由冰晶与白玉构成，阵座周围寒雾凝而不散。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F38" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19005.png</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="str">
+        <x:v>寒谷背阴处所见的冰晶阵座由冰晶与白玉构成，阵座周围寒雾凝而不散。</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -25296,10 +30255,8 @@
       <x:c r="B39" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C39" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火演阵台</x:t>
-        </x:is>
+      <x:c r="C39" s="3" t="str">
+        <x:v>离火演阵台</x:v>
       </x:c>
       <x:c r="D39" s="3" t="n">
         <x:v>33</x:v>
@@ -25307,20 +30264,14 @@
       <x:c r="E39" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F39" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19006.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G39" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火演阵台以离火石与赤砂筑成，赤线在台面缓缓游动。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H39" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F39" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19006.png</x:v>
+      </x:c>
+      <x:c r="G39" s="3" t="str">
+        <x:v>离火演阵台以离火石与赤砂筑成，赤线在台面缓缓游动。</x:v>
+      </x:c>
+      <x:c r="H39" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -25330,10 +30281,8 @@
       <x:c r="B40" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C40" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玉阵盘</x:t>
-        </x:is>
+      <x:c r="C40" s="3" t="str">
+        <x:v>青玉阵盘</x:v>
       </x:c>
       <x:c r="D40" s="3" t="n">
         <x:v>33</x:v>
@@ -25341,20 +30290,14 @@
       <x:c r="E40" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F40" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19007.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G40" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玉阵盘立于苍梧秘境，玉盘内部似有云海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H40" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F40" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19007.png</x:v>
+      </x:c>
+      <x:c r="G40" s="3" t="str">
+        <x:v>青玉阵盘立于苍梧秘境，玉盘内部似有云海。</x:v>
+      </x:c>
+      <x:c r="H40" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -25364,10 +30307,8 @@
       <x:c r="B41" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C41" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷纹阵枢</x:t>
-        </x:is>
+      <x:c r="C41" s="3" t="str">
+        <x:v>雷纹阵枢</x:v>
       </x:c>
       <x:c r="D41" s="3" t="n">
         <x:v>33</x:v>
@@ -25375,20 +30316,14 @@
       <x:c r="E41" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F41" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19008.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G41" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取雷纹晶与玄铜建成雷纹阵枢，枢心转动时隐闻雷声。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H41" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F41" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19008.png</x:v>
+      </x:c>
+      <x:c r="G41" s="3" t="str">
+        <x:v>匠人取雷纹晶与玄铜建成雷纹阵枢，枢心转动时隐闻雷声。</x:v>
+      </x:c>
+      <x:c r="H41" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -25398,10 +30333,8 @@
       <x:c r="B42" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉阵坛</x:t>
-        </x:is>
+      <x:c r="C42" s="3" t="str">
+        <x:v>地脉阵坛</x:v>
       </x:c>
       <x:c r="D42" s="3" t="n">
         <x:v>33</x:v>
@@ -25409,20 +30342,14 @@
       <x:c r="E42" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19009.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻地脉阵坛旧址在坤元地脉，地脉气息沿阵枢缓缓升起。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F42" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19009.png</x:v>
+      </x:c>
+      <x:c r="G42" s="3" t="str">
+        <x:v>传闻地脉阵坛旧址在坤元地脉，地脉气息沿阵枢缓缓升起。</x:v>
+      </x:c>
+      <x:c r="H42" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -25432,10 +30359,8 @@
       <x:c r="B43" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C43" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星罗演天台</x:t>
-        </x:is>
+      <x:c r="C43" s="3" t="str">
+        <x:v>星罗演天台</x:v>
       </x:c>
       <x:c r="D43" s="3" t="n">
         <x:v>33</x:v>
@@ -25443,20 +30368,14 @@
       <x:c r="E43" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F43" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19010.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G43" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星落天原所见的星罗演天台由星陨铁与天河砂构成，夜间阵枢会映出群星轨迹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F43" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19010.png</x:v>
+      </x:c>
+      <x:c r="G43" s="3" t="str">
+        <x:v>星落天原所见的星罗演天台由星陨铁与天河砂构成，夜间阵枢会映出群星轨迹。</x:v>
+      </x:c>
+      <x:c r="H43" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -25466,10 +30385,8 @@
       <x:c r="B44" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C44" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟幻阵台</x:t>
-        </x:is>
+      <x:c r="C44" s="3" t="str">
+        <x:v>紫烟幻阵台</x:v>
       </x:c>
       <x:c r="D44" s="3" t="n">
         <x:v>33</x:v>
@@ -25477,20 +30394,14 @@
       <x:c r="E44" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F44" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19011.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G44" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟幻阵台以紫府玉与烟霞木筑成，紫色云烟常在阵枢周围盘旋。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H44" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F44" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19011.png</x:v>
+      </x:c>
+      <x:c r="G44" s="3" t="str">
+        <x:v>紫烟幻阵台以紫府玉与烟霞木筑成，紫色云烟常在阵枢周围盘旋。</x:v>
+      </x:c>
+      <x:c r="H44" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -25500,10 +30411,8 @@
       <x:c r="B45" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C45" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九曲阵宫</x:t>
-        </x:is>
+      <x:c r="C45" s="3" t="str">
+        <x:v>九曲阵宫</x:v>
       </x:c>
       <x:c r="D45" s="3" t="n">
         <x:v>33</x:v>
@@ -25511,20 +30420,14 @@
       <x:c r="E45" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F45" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19012.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G45" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九曲阵宫立于九曲地宫，阵枢依九曲方位层层展开。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H45" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F45" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19012.png</x:v>
+      </x:c>
+      <x:c r="G45" s="3" t="str">
+        <x:v>九曲阵宫立于九曲地宫，阵枢依九曲方位层层展开。</x:v>
+      </x:c>
+      <x:c r="H45" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -25534,10 +30437,8 @@
       <x:c r="B46" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C46" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅火阵坛</x:t>
-        </x:is>
+      <x:c r="C46" s="3" t="str">
+        <x:v>涅火阵坛</x:v>
       </x:c>
       <x:c r="D46" s="3" t="n">
         <x:v>33</x:v>
@@ -25545,20 +30446,14 @@
       <x:c r="E46" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F46" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19013.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取涅火晶与赤金建成涅火阵坛，赤金纹路随天火明灭不定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F46" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19013.png</x:v>
+      </x:c>
+      <x:c r="G46" s="3" t="str">
+        <x:v>匠人取涅火晶与赤金建成涅火阵坛，赤金纹路随天火明灭不定。</x:v>
+      </x:c>
+      <x:c r="H46" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -25568,10 +30463,8 @@
       <x:c r="B47" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C47" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙纹天盘</x:t>
-        </x:is>
+      <x:c r="C47" s="3" t="str">
+        <x:v>龙纹天盘</x:v>
       </x:c>
       <x:c r="D47" s="3" t="n">
         <x:v>33</x:v>
@@ -25579,20 +30472,14 @@
       <x:c r="E47" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F47" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19014.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G47" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻龙纹天盘旧址在龙眠古渊，阵枢上隐约盘着龙形云气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H47" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F47" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19014.png</x:v>
+      </x:c>
+      <x:c r="G47" s="3" t="str">
+        <x:v>传闻龙纹天盘旧址在龙眠古渊，阵枢上隐约盘着龙形云气。</x:v>
+      </x:c>
+      <x:c r="H47" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -25602,10 +30489,8 @@
       <x:c r="B48" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C48" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽阵架</x:t>
-        </x:is>
+      <x:c r="C48" s="3" t="str">
+        <x:v>凤羽阵架</x:v>
       </x:c>
       <x:c r="D48" s="3" t="n">
         <x:v>33</x:v>
@@ -25613,20 +30498,14 @@
       <x:c r="E48" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F48" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19015.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G48" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖神木所见的凤羽阵架由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H48" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F48" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19015.png</x:v>
+      </x:c>
+      <x:c r="G48" s="3" t="str">
+        <x:v>凤栖神木所见的凤羽阵架由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:v>
+      </x:c>
+      <x:c r="H48" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -25636,10 +30515,8 @@
       <x:c r="B49" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C49" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太一阵道台</x:t>
-        </x:is>
+      <x:c r="C49" s="3" t="str">
+        <x:v>太一阵道台</x:v>
       </x:c>
       <x:c r="D49" s="3" t="n">
         <x:v>33</x:v>
@@ -25647,20 +30524,14 @@
       <x:c r="E49" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F49" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/19016.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G49" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太一阵道台以太初晶与鸿蒙母金筑成，近看阵枢仿佛隔着太初雾海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182</x:t>
-        </x:is>
+      <x:c r="F49" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/19016.png</x:v>
+      </x:c>
+      <x:c r="G49" s="3" t="str">
+        <x:v>太一阵道台以太初晶与鸿蒙母金筑成，近看阵枢仿佛隔着太初雾海。</x:v>
+      </x:c>
+      <x:c r="H49" s="3" t="str">
+        <x:v>167;168;169;170;171;172;173;174;175;176;177;178;179;180;181;182;241;242;243;244;245;246;247;248;249;250</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -25670,10 +30541,8 @@
       <x:c r="B50" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C50" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松板画符桌</x:t>
-        </x:is>
+      <x:c r="C50" s="3" t="str">
+        <x:v>松板画符桌</x:v>
       </x:c>
       <x:c r="D50" s="3" t="n">
         <x:v>34</x:v>
@@ -25681,20 +30550,14 @@
       <x:c r="E50" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F50" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20001.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G50" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松板画符桌以松板与竹骨筑成，桌面留有淡墨旧痕。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H50" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F50" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20001.png</x:v>
+      </x:c>
+      <x:c r="G50" s="3" t="str">
+        <x:v>松板画符桌以松板与竹骨筑成，桌面留有淡墨旧痕。</x:v>
+      </x:c>
+      <x:c r="H50" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -25704,10 +30567,8 @@
       <x:c r="B51" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C51" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青石符案</x:t>
-        </x:is>
+      <x:c r="C51" s="3" t="str">
+        <x:v>青石符案</x:v>
       </x:c>
       <x:c r="D51" s="3" t="n">
         <x:v>34</x:v>
@@ -25715,20 +30576,14 @@
       <x:c r="E51" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F51" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20002.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G51" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青石符案立于溪谷缓坡，符案边缘生着青苔纹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H51" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F51" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20002.png</x:v>
+      </x:c>
+      <x:c r="G51" s="3" t="str">
+        <x:v>青石符案立于溪谷缓坡，符案边缘生着青苔纹。</x:v>
+      </x:c>
+      <x:c r="H51" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -25738,10 +30593,8 @@
       <x:c r="B52" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤铜镇符台</x:t>
-        </x:is>
+      <x:c r="C52" s="3" t="str">
+        <x:v>赤铜镇符台</x:v>
       </x:c>
       <x:c r="D52" s="3" t="n">
         <x:v>34</x:v>
@@ -25749,20 +30602,14 @@
       <x:c r="E52" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20003.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取赤铜与白石建成赤铜镇符台，镇角铜兽静伏四方。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F52" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20003.png</x:v>
+      </x:c>
+      <x:c r="G52" s="3" t="str">
+        <x:v>匠人取赤铜与白石建成赤铜镇符台，镇角铜兽静伏四方。</x:v>
+      </x:c>
+      <x:c r="H52" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -25772,10 +30619,8 @@
       <x:c r="B53" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄铁符桌</x:t>
-        </x:is>
+      <x:c r="C53" s="3" t="str">
+        <x:v>玄铁符桌</x:v>
       </x:c>
       <x:c r="D53" s="3" t="n">
         <x:v>34</x:v>
@@ -25783,20 +30628,14 @@
       <x:c r="E53" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20004.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻玄铁符桌旧址在云崖石台，铁桌表面平整如镜。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F53" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20004.png</x:v>
+      </x:c>
+      <x:c r="G53" s="3" t="str">
+        <x:v>传闻玄铁符桌旧址在云崖石台，铁桌表面平整如镜。</x:v>
+      </x:c>
+      <x:c r="H53" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -25806,10 +30645,8 @@
       <x:c r="B54" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰晶画案</x:t>
-        </x:is>
+      <x:c r="C54" s="3" t="str">
+        <x:v>冰晶画案</x:v>
       </x:c>
       <x:c r="D54" s="3" t="n">
         <x:v>34</x:v>
@@ -25817,20 +30654,14 @@
       <x:c r="E54" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20005.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒谷背阴处所见的冰晶画案由冰晶与寒木构成，画案周围常有白雾。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F54" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20005.png</x:v>
+      </x:c>
+      <x:c r="G54" s="3" t="str">
+        <x:v>寒谷背阴处所见的冰晶画案由冰晶与寒木构成，画案周围常有白雾。</x:v>
+      </x:c>
+      <x:c r="H54" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -25840,10 +30671,8 @@
       <x:c r="B55" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火符台</x:t>
-        </x:is>
+      <x:c r="C55" s="3" t="str">
+        <x:v>离火符台</x:v>
       </x:c>
       <x:c r="D55" s="3" t="n">
         <x:v>34</x:v>
@@ -25851,20 +30680,14 @@
       <x:c r="E55" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20006.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离火符台以离火石与朱砂筑成，台心朱砂经年不褪。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F55" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20006.png</x:v>
+      </x:c>
+      <x:c r="G55" s="3" t="str">
+        <x:v>离火符台以离火石与朱砂筑成，台心朱砂经年不褪。</x:v>
+      </x:c>
+      <x:c r="H55" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -25874,10 +30697,8 @@
       <x:c r="B56" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玉符案</x:t>
-        </x:is>
+      <x:c r="C56" s="3" t="str">
+        <x:v>青玉符案</x:v>
       </x:c>
       <x:c r="D56" s="3" t="n">
         <x:v>34</x:v>
@@ -25885,20 +30706,14 @@
       <x:c r="E56" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20007.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玉符案立于苍梧秘境，玉案内藏天然云纹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F56" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20007.png</x:v>
+      </x:c>
+      <x:c r="G56" s="3" t="str">
+        <x:v>青玉符案立于苍梧秘境，玉案内藏天然云纹。</x:v>
+      </x:c>
+      <x:c r="H56" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -25908,10 +30723,8 @@
       <x:c r="B57" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷砂画台</x:t>
-        </x:is>
+      <x:c r="C57" s="3" t="str">
+        <x:v>雷砂画台</x:v>
       </x:c>
       <x:c r="D57" s="3" t="n">
         <x:v>34</x:v>
@@ -25919,20 +30732,14 @@
       <x:c r="E57" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20008.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取雷砂与紫铜建成雷砂画台，落笔时偶有雷光沿线游走。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F57" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20008.png</x:v>
+      </x:c>
+      <x:c r="G57" s="3" t="str">
+        <x:v>匠人取雷砂与紫铜建成雷砂画台，落笔时偶有雷光沿线游走。</x:v>
+      </x:c>
+      <x:c r="H57" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -25942,10 +30749,8 @@
       <x:c r="B58" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉符桌</x:t>
-        </x:is>
+      <x:c r="C58" s="3" t="str">
+        <x:v>地脉符桌</x:v>
       </x:c>
       <x:c r="D58" s="3" t="n">
         <x:v>34</x:v>
@@ -25953,20 +30758,14 @@
       <x:c r="E58" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20009.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻地脉符桌旧址在坤元地脉，地脉气息沿案面缓缓升起。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F58" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20009.png</x:v>
+      </x:c>
+      <x:c r="G58" s="3" t="str">
+        <x:v>传闻地脉符桌旧址在坤元地脉，地脉气息沿案面缓缓升起。</x:v>
+      </x:c>
+      <x:c r="H58" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -25976,10 +30775,8 @@
       <x:c r="B59" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星纹画阁</x:t>
-        </x:is>
+      <x:c r="C59" s="3" t="str">
+        <x:v>星纹画阁</x:v>
       </x:c>
       <x:c r="D59" s="3" t="n">
         <x:v>34</x:v>
@@ -25987,20 +30784,14 @@
       <x:c r="E59" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20010.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星落天原所见的星纹画阁由星陨铁与天河砂构成，夜间案面会映出群星轨迹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F59" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20010.png</x:v>
+      </x:c>
+      <x:c r="G59" s="3" t="str">
+        <x:v>星落天原所见的星纹画阁由星陨铁与天河砂构成，夜间案面会映出群星轨迹。</x:v>
+      </x:c>
+      <x:c r="H59" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -26010,10 +30801,8 @@
       <x:c r="B60" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟符殿</x:t>
-        </x:is>
+      <x:c r="C60" s="3" t="str">
+        <x:v>紫烟符殿</x:v>
       </x:c>
       <x:c r="D60" s="3" t="n">
         <x:v>34</x:v>
@@ -26021,20 +30810,14 @@
       <x:c r="E60" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20011.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟符殿以紫府玉与烟霞木筑成，紫色云烟常在案面周围盘旋。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F60" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20011.png</x:v>
+      </x:c>
+      <x:c r="G60" s="3" t="str">
+        <x:v>紫烟符殿以紫府玉与烟霞木筑成，紫色云烟常在案面周围盘旋。</x:v>
+      </x:c>
+      <x:c r="H60" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -26044,10 +30827,8 @@
       <x:c r="B61" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍符案</x:t>
-        </x:is>
+      <x:c r="C61" s="3" t="str">
+        <x:v>九窍符案</x:v>
       </x:c>
       <x:c r="D61" s="3" t="n">
         <x:v>34</x:v>
@@ -26055,20 +30836,14 @@
       <x:c r="E61" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20012.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍符案立于九曲地宫，案面依九曲方位层层展开。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F61" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20012.png</x:v>
+      </x:c>
+      <x:c r="G61" s="3" t="str">
+        <x:v>九窍符案立于九曲地宫，案面依九曲方位层层展开。</x:v>
+      </x:c>
+      <x:c r="H61" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -26078,10 +30853,8 @@
       <x:c r="B62" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅火符台</x:t>
-        </x:is>
+      <x:c r="C62" s="3" t="str">
+        <x:v>涅火符台</x:v>
       </x:c>
       <x:c r="D62" s="3" t="n">
         <x:v>34</x:v>
@@ -26089,20 +30862,14 @@
       <x:c r="E62" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F62" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20013.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G62" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取涅火晶与赤金建成涅火符台，赤金纹路随天火明灭不定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H62" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F62" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20013.png</x:v>
+      </x:c>
+      <x:c r="G62" s="3" t="str">
+        <x:v>匠人取涅火晶与赤金建成涅火符台，赤金纹路随天火明灭不定。</x:v>
+      </x:c>
+      <x:c r="H62" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -26112,10 +30879,8 @@
       <x:c r="B63" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙皮天案</x:t>
-        </x:is>
+      <x:c r="C63" s="3" t="str">
+        <x:v>龙皮天案</x:v>
       </x:c>
       <x:c r="D63" s="3" t="n">
         <x:v>34</x:v>
@@ -26123,20 +30888,14 @@
       <x:c r="E63" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20014.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻龙皮天案旧址在龙眠古渊，案面上隐约盘着龙形云气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F63" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20014.png</x:v>
+      </x:c>
+      <x:c r="G63" s="3" t="str">
+        <x:v>传闻龙皮天案旧址在龙眠古渊，案面上隐约盘着龙形云气。</x:v>
+      </x:c>
+      <x:c r="H63" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -26146,10 +30905,8 @@
       <x:c r="B64" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽画台</x:t>
-        </x:is>
+      <x:c r="C64" s="3" t="str">
+        <x:v>凤羽画台</x:v>
       </x:c>
       <x:c r="D64" s="3" t="n">
         <x:v>34</x:v>
@@ -26157,20 +30914,14 @@
       <x:c r="E64" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20015.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖神木所见的凤羽画台由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F64" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20015.png</x:v>
+      </x:c>
+      <x:c r="G64" s="3" t="str">
+        <x:v>凤栖神木所见的凤羽画台由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:v>
+      </x:c>
+      <x:c r="H64" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -26180,10 +30931,8 @@
       <x:c r="B65" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初符道台</x:t>
-        </x:is>
+      <x:c r="C65" s="3" t="str">
+        <x:v>太初符道台</x:v>
       </x:c>
       <x:c r="D65" s="3" t="n">
         <x:v>34</x:v>
@@ -26191,20 +30940,14 @@
       <x:c r="E65" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/20016.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初符道台以太初晶与鸿蒙母金筑成，近看案面仿佛隔着太初雾海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198</x:t>
-        </x:is>
+      <x:c r="F65" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/20016.png</x:v>
+      </x:c>
+      <x:c r="G65" s="3" t="str">
+        <x:v>太初符道台以太初晶与鸿蒙母金筑成，近看案面仿佛隔着太初雾海。</x:v>
+      </x:c>
+      <x:c r="H65" s="3" t="str">
+        <x:v>183;184;185;186;187;188;189;190;191;192;193;194;195;196;197;198;251;252;253;254;255;256;257;258;259;260</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -26214,10 +30957,8 @@
       <x:c r="B66" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">陶瓮酒坊</x:t>
-        </x:is>
+      <x:c r="C66" s="3" t="str">
+        <x:v>陶瓮酒坊</x:v>
       </x:c>
       <x:c r="D66" s="3" t="n">
         <x:v>35</x:v>
@@ -26225,20 +30966,14 @@
       <x:c r="E66" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21001.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">陶瓮酒坊以陶瓮与松木筑成，坊中常有淡淡谷香。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F66" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21001.png</x:v>
+      </x:c>
+      <x:c r="G66" s="3" t="str">
+        <x:v>陶瓮酒坊以陶瓮与松木筑成，坊中常有淡淡谷香。</x:v>
+      </x:c>
+      <x:c r="H66" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -26248,10 +30983,8 @@
       <x:c r="B67" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松桶酒窖</x:t>
-        </x:is>
+      <x:c r="C67" s="3" t="str">
+        <x:v>松桶酒窖</x:v>
       </x:c>
       <x:c r="D67" s="3" t="n">
         <x:v>35</x:v>
@@ -26259,20 +30992,14 @@
       <x:c r="E67" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21002.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">松桶酒窖立于溪谷缓坡，酒窖木壁沁着陈年香气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F67" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21002.png</x:v>
+      </x:c>
+      <x:c r="G67" s="3" t="str">
+        <x:v>松桶酒窖立于溪谷缓坡，酒窖木壁沁着陈年香气。</x:v>
+      </x:c>
+      <x:c r="H67" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -26282,10 +31009,8 @@
       <x:c r="B68" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">铜甑酒灶</x:t>
-        </x:is>
+      <x:c r="C68" s="3" t="str">
+        <x:v>铜甑酒灶</x:v>
       </x:c>
       <x:c r="D68" s="3" t="n">
         <x:v>35</x:v>
@@ -26293,20 +31018,14 @@
       <x:c r="E68" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21003.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取铜甑与青砖建成铜甑酒灶，铜甑上蒸汽盘旋如云。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F68" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21003.png</x:v>
+      </x:c>
+      <x:c r="G68" s="3" t="str">
+        <x:v>匠人取铜甑与青砖建成铜甑酒灶，铜甑上蒸汽盘旋如云。</x:v>
+      </x:c>
+      <x:c r="H68" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -26316,10 +31035,8 @@
       <x:c r="B69" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄铁酒库</x:t>
-        </x:is>
+      <x:c r="C69" s="3" t="str">
+        <x:v>玄铁酒库</x:v>
       </x:c>
       <x:c r="D69" s="3" t="n">
         <x:v>35</x:v>
@@ -26327,20 +31044,14 @@
       <x:c r="E69" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21004.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻玄铁酒库旧址在云崖石台，铁瓮封口覆着古旧泥印。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F69" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21004.png</x:v>
+      </x:c>
+      <x:c r="G69" s="3" t="str">
+        <x:v>传闻玄铁酒库旧址在云崖石台，铁瓮封口覆着古旧泥印。</x:v>
+      </x:c>
+      <x:c r="H69" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -26350,10 +31061,8 @@
       <x:c r="B70" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰窟酒坊</x:t>
-        </x:is>
+      <x:c r="C70" s="3" t="str">
+        <x:v>冰窟酒坊</x:v>
       </x:c>
       <x:c r="D70" s="3" t="n">
         <x:v>35</x:v>
@@ -26361,20 +31070,14 @@
       <x:c r="E70" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21005.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒谷背阴处所见的冰窟酒坊由冰岩与寒木构成，窟壁凝霜而酒香不散。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F70" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21005.png</x:v>
+      </x:c>
+      <x:c r="G70" s="3" t="str">
+        <x:v>寒谷背阴处所见的冰窟酒坊由冰岩与寒木构成，窟壁凝霜而酒香不散。</x:v>
+      </x:c>
+      <x:c r="H70" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -26384,10 +31087,8 @@
       <x:c r="B71" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地火酒灶</x:t>
-        </x:is>
+      <x:c r="C71" s="3" t="str">
+        <x:v>地火酒灶</x:v>
       </x:c>
       <x:c r="D71" s="3" t="n">
         <x:v>35</x:v>
@@ -26395,20 +31096,14 @@
       <x:c r="E71" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21006.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地火酒灶以地火石与赤铜筑成，灶下余火昼夜微明。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F71" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21006.png</x:v>
+      </x:c>
+      <x:c r="G71" s="3" t="str">
+        <x:v>地火酒灶以地火石与赤铜筑成，灶下余火昼夜微明。</x:v>
+      </x:c>
+      <x:c r="H71" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -26418,10 +31113,8 @@
       <x:c r="B72" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青藤酒架</x:t>
-        </x:is>
+      <x:c r="C72" s="3" t="str">
+        <x:v>青藤酒架</x:v>
       </x:c>
       <x:c r="D72" s="3" t="n">
         <x:v>35</x:v>
@@ -26429,20 +31122,14 @@
       <x:c r="E72" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21007.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青藤酒架立于苍梧秘境，藤叶间悬着细小露珠。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F72" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21007.png</x:v>
+      </x:c>
+      <x:c r="G72" s="3" t="str">
+        <x:v>青藤酒架立于苍梧秘境，藤叶间悬着细小露珠。</x:v>
+      </x:c>
+      <x:c r="H72" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -26452,10 +31139,8 @@
       <x:c r="B73" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷纹酒瓮</x:t>
-        </x:is>
+      <x:c r="C73" s="3" t="str">
+        <x:v>雷纹酒瓮</x:v>
       </x:c>
       <x:c r="D73" s="3" t="n">
         <x:v>35</x:v>
@@ -26463,20 +31148,14 @@
       <x:c r="E73" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21008.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取雷纹陶与黑石建成雷纹酒瓮，雨夜瓮身会发出轻鸣。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F73" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21008.png</x:v>
+      </x:c>
+      <x:c r="G73" s="3" t="str">
+        <x:v>匠人取雷纹陶与黑石建成雷纹酒瓮，雨夜瓮身会发出轻鸣。</x:v>
+      </x:c>
+      <x:c r="H73" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -26486,10 +31165,8 @@
       <x:c r="B74" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉酒窖</x:t>
-        </x:is>
+      <x:c r="C74" s="3" t="str">
+        <x:v>地脉酒窖</x:v>
       </x:c>
       <x:c r="D74" s="3" t="n">
         <x:v>35</x:v>
@@ -26497,20 +31174,14 @@
       <x:c r="E74" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21009.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻地脉酒窖旧址在坤元地脉，地脉气息沿酒瓮缓缓升起。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F74" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21009.png</x:v>
+      </x:c>
+      <x:c r="G74" s="3" t="str">
+        <x:v>传闻地脉酒窖旧址在坤元地脉，地脉气息沿酒瓮缓缓升起。</x:v>
+      </x:c>
+      <x:c r="H74" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -26520,10 +31191,8 @@
       <x:c r="B75" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星露酿坊</x:t>
-        </x:is>
+      <x:c r="C75" s="3" t="str">
+        <x:v>星露酿坊</x:v>
       </x:c>
       <x:c r="D75" s="3" t="n">
         <x:v>35</x:v>
@@ -26531,20 +31200,14 @@
       <x:c r="E75" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21010.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星落天原所见的星露酿坊由星陨铁与天河砂构成，夜间酒瓮会映出群星轨迹。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F75" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21010.png</x:v>
+      </x:c>
+      <x:c r="G75" s="3" t="str">
+        <x:v>星落天原所见的星露酿坊由星陨铁与天河砂构成，夜间酒瓮会映出群星轨迹。</x:v>
+      </x:c>
+      <x:c r="H75" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -26554,10 +31217,8 @@
       <x:c r="B76" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟酒殿</x:t>
-        </x:is>
+      <x:c r="C76" s="3" t="str">
+        <x:v>紫烟酒殿</x:v>
       </x:c>
       <x:c r="D76" s="3" t="n">
         <x:v>35</x:v>
@@ -26565,20 +31226,14 @@
       <x:c r="E76" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21011.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫烟酒殿以紫府玉与烟霞木筑成，紫色云烟常在酒瓮周围盘旋。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F76" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21011.png</x:v>
+      </x:c>
+      <x:c r="G76" s="3" t="str">
+        <x:v>紫烟酒殿以紫府玉与烟霞木筑成，紫色云烟常在酒瓮周围盘旋。</x:v>
+      </x:c>
+      <x:c r="H76" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -26588,10 +31243,8 @@
       <x:c r="B77" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九曲酒池</x:t>
-        </x:is>
+      <x:c r="C77" s="3" t="str">
+        <x:v>九曲酒池</x:v>
       </x:c>
       <x:c r="D77" s="3" t="n">
         <x:v>35</x:v>
@@ -26599,20 +31252,14 @@
       <x:c r="E77" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21012.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九曲酒池立于九曲地宫，酒瓮依九曲方位层层展开。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F77" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21012.png</x:v>
+      </x:c>
+      <x:c r="G77" s="3" t="str">
+        <x:v>九曲酒池立于九曲地宫，酒瓮依九曲方位层层展开。</x:v>
+      </x:c>
+      <x:c r="H77" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -26622,10 +31269,8 @@
       <x:c r="B78" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅火酒炉</x:t>
-        </x:is>
+      <x:c r="C78" s="3" t="str">
+        <x:v>涅火酒炉</x:v>
       </x:c>
       <x:c r="D78" s="3" t="n">
         <x:v>35</x:v>
@@ -26633,20 +31278,14 @@
       <x:c r="E78" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21013.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">匠人取涅火晶与赤金建成涅火酒炉，赤金纹路随天火明灭不定。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F78" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21013.png</x:v>
+      </x:c>
+      <x:c r="G78" s="3" t="str">
+        <x:v>匠人取涅火晶与赤金建成涅火酒炉，赤金纹路随天火明灭不定。</x:v>
+      </x:c>
+      <x:c r="H78" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -26656,10 +31295,8 @@
       <x:c r="B79" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙涎酒宫</x:t>
-        </x:is>
+      <x:c r="C79" s="3" t="str">
+        <x:v>龙涎酒宫</x:v>
       </x:c>
       <x:c r="D79" s="3" t="n">
         <x:v>35</x:v>
@@ -26667,20 +31304,14 @@
       <x:c r="E79" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21014.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">传闻龙涎酒宫旧址在龙眠古渊，酒瓮上隐约盘着龙形云气。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F79" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21014.png</x:v>
+      </x:c>
+      <x:c r="G79" s="3" t="str">
+        <x:v>传闻龙涎酒宫旧址在龙眠古渊，酒瓮上隐约盘着龙形云气。</x:v>
+      </x:c>
+      <x:c r="H79" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -26690,10 +31321,8 @@
       <x:c r="B80" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖酿坊</x:t>
-        </x:is>
+      <x:c r="C80" s="3" t="str">
+        <x:v>凤栖酿坊</x:v>
       </x:c>
       <x:c r="D80" s="3" t="n">
         <x:v>35</x:v>
@@ -26701,20 +31330,14 @@
       <x:c r="E80" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21015.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤栖神木所见的凤栖酿坊由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F80" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21015.png</x:v>
+      </x:c>
+      <x:c r="G80" s="3" t="str">
+        <x:v>凤栖神木所见的凤栖酿坊由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</x:v>
+      </x:c>
+      <x:c r="H80" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -26724,10 +31347,8 @@
       <x:c r="B81" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初酒鼎</x:t>
-        </x:is>
+      <x:c r="C81" s="3" t="str">
+        <x:v>太初酒鼎</x:v>
       </x:c>
       <x:c r="D81" s="3" t="n">
         <x:v>35</x:v>
@@ -26735,20 +31356,14 @@
       <x:c r="E81" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">res://assets/items/icons_simple/21016.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太初酒鼎以太初晶与鸿蒙母金筑成，近看酒瓮仿佛隔着太初雾海。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150</x:t>
-        </x:is>
+      <x:c r="F81" s="3" t="str">
+        <x:v>res://assets/items/icons_simple/21016.png</x:v>
+      </x:c>
+      <x:c r="G81" s="3" t="str">
+        <x:v>太初酒鼎以太初晶与鸿蒙母金筑成，近看酒瓮仿佛隔着太初雾海。</x:v>
+      </x:c>
+      <x:c r="H81" s="3" t="str">
+        <x:v>101;102;103;104;105;106;107;108;109;110;111;112;113;114;115;116;117;118;119;120;121;122;123;124;125;126;127;128;129;130;131;132;133;134;135;136;137;138;139;140;141;142;143;144;145;146;147;148;149;150;221;222;223;224;225;226;227;228;229;230</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
